--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V1\cartera-cpel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41DB1E0-6892-4E5A-BE6F-DFDC9D3CCA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AEE5E2-6E0F-4D00-9CA8-C703BC0F25A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BO$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="209">
   <si>
     <t>id</t>
   </si>
@@ -486,9 +499,6 @@
     <t>23/10/2027</t>
   </si>
   <si>
-    <t>01/12/2028</t>
-  </si>
-  <si>
     <t>Kaplan tipo "S"</t>
   </si>
   <si>
@@ -621,13 +631,73 @@
   <si>
     <t>•	Obra Civil: La CFE y la Secretaría de Obras Públicas del Estado de Sinaloa atienden los compromisos para la entrega de las obras civiles y están a la espera de que la dependencia confirme la fecha para el cierre administrativo y el finiquito de los contratos.
 •	Obra Electromecánica: Conciliar las Razones Fundadas y Explicitas y celebrar con el Contratista Andritz el Primer Convenio Modificatorio del Contrato No. F/10670-021/2024 de la Obra Electromecánica.</t>
+  </si>
+  <si>
+    <t>30/12/2028</t>
+  </si>
+  <si>
+    <t>Limpieza y nivelación del 50% de área del polígono del Parque Fotovoltaico</t>
+  </si>
+  <si>
+    <t>20/05/26</t>
+  </si>
+  <si>
+    <t>08/08/26</t>
+  </si>
+  <si>
+    <t>$14,700,350.00</t>
+  </si>
+  <si>
+    <t>Entrega de Ingeniería Civil de detalle rev0 aprobada sin comentarios por la CFE</t>
+  </si>
+  <si>
+    <t>Limpieza y Nivelación al 100 % de área del polígono del Parque Fotovoltaico.</t>
+  </si>
+  <si>
+    <t>$**,***,***</t>
+  </si>
+  <si>
+    <t>19/07/26</t>
+  </si>
+  <si>
+    <t>Llegada a Sitio del 100% del Sistema de seguimiento (hincas y Trackers) y Equipos de acondicionamiento de potencia (Inversores)</t>
+  </si>
+  <si>
+    <t>$17,200,000.00</t>
+  </si>
+  <si>
+    <t>14/05/26</t>
+  </si>
+  <si>
+    <t>Entrega de Ingeniería Conceptual aprobada sin comentarios por la CFE</t>
+  </si>
+  <si>
+    <t>$34,400,000.00</t>
+  </si>
+  <si>
+    <t>24/05/26</t>
+  </si>
+  <si>
+    <t>Conclusión de movilización a Sitio Terminada (vallado perimetral de las oficinas temporales del área de almacén).</t>
+  </si>
+  <si>
+    <t>23/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega de Ingeniería Civil de detalle rev0 aprobada sin comentarios por la CFE </t>
+  </si>
+  <si>
+    <t>21/09/26</t>
+  </si>
+  <si>
+    <t>Colocación de Órdenes de Compra de equipos electromecánicos del Parque Fotovoltaico</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,19 +728,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -698,12 +776,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -887,6 +965,58 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -899,50 +1029,53 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1251,7 +1384,7 @@
   <dimension ref="A1:BO7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1311,1068 +1444,1132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="18" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="18" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="18" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="18" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="18" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="18" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="18" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="18" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="18" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="18" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="18" t="s">
+      <c r="AF1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AG1" s="17" t="s">
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="17" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="17" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="17" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AK1" s="17" t="s">
+      <c r="AK1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AL1" s="17" t="s">
+      <c r="AL1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AM1" s="17" t="s">
+      <c r="AM1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AN1" s="17" t="s">
+      <c r="AN1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AO1" s="17" t="s">
+      <c r="AO1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AP1" s="17" t="s">
+      <c r="AP1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AQ1" s="19" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AR1" s="19" t="s">
+      <c r="AR1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AS1" s="19" t="s">
+      <c r="AS1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AT1" s="19" t="s">
+      <c r="AT1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="19" t="s">
+      <c r="AU1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="19" t="s">
+      <c r="AV1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AW1" s="19" t="s">
+      <c r="AW1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AX1" s="19" t="s">
+      <c r="AX1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AY1" s="19" t="s">
+      <c r="AY1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AZ1" s="19" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="BA1" s="19" t="s">
+      <c r="BA1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="BB1" s="19" t="s">
+      <c r="BB1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="BC1" s="19" t="s">
+      <c r="BC1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="BD1" s="19" t="s">
+      <c r="BD1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="BE1" s="19" t="s">
+      <c r="BE1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="BF1" s="19" t="s">
+      <c r="BF1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="BG1" s="19" t="s">
+      <c r="BG1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="BH1" s="19" t="s">
+      <c r="BH1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="BI1" s="19" t="s">
+      <c r="BI1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="BJ1" s="19" t="s">
+      <c r="BJ1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="BK1" s="19" t="s">
+      <c r="BK1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="BL1" s="19" t="s">
+      <c r="BL1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BM1" s="19" t="s">
+      <c r="BM1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="BN1" s="19" t="s">
+      <c r="BN1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="BO1" s="20" t="s">
+      <c r="BO1" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A2" s="21">
+      <c r="A2" s="25">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="7">
         <v>30.76</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="7">
         <v>27.79</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="7">
         <v>6.05</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="7">
         <v>5.29</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="7">
         <v>16.350000000000001</v>
       </c>
-      <c r="K2" s="24">
+      <c r="K2" s="7">
         <v>16.34</v>
       </c>
-      <c r="L2" s="24">
+      <c r="L2" s="7">
         <v>8.36</v>
       </c>
-      <c r="M2" s="24">
+      <c r="M2" s="7">
         <v>6.16</v>
       </c>
-      <c r="N2" s="24">
+      <c r="N2" s="7">
         <v>0</v>
       </c>
-      <c r="O2" s="24">
+      <c r="O2" s="7">
         <v>0</v>
       </c>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="AG2" s="22" t="s">
+      <c r="P2" s="7">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="R2" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="T2" s="7">
+        <v>5</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="X2" s="7">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>8</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE2" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="AF2" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="AG2" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AH2" s="22" t="s">
+      <c r="AH2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AI2" s="22" t="s">
+      <c r="AI2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AJ2" s="22">
+      <c r="AJ2" s="10">
         <v>728</v>
       </c>
-      <c r="AK2" s="22" t="s">
+      <c r="AK2" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AL2" s="26" t="s">
+      <c r="AL2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="AM2" s="26" t="s">
+      <c r="AM2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="AN2" s="26" t="s">
+      <c r="AN2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="AO2" s="26" t="s">
+      <c r="AO2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="AP2" s="26" t="s">
+      <c r="AP2" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="AQ2" s="26" t="s">
+      <c r="AQ2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AR2" s="26" t="s">
+      <c r="AR2" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AS2" s="26" t="s">
+      <c r="AS2" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AT2" s="26" t="s">
+      <c r="AT2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AU2" s="26" t="s">
+      <c r="AU2" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AV2" s="26" t="s">
+      <c r="AV2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AW2" s="22" t="s">
+      <c r="AW2" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="26" t="s">
+      <c r="AX2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AY2" s="26" t="s">
+      <c r="AY2" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AZ2" s="26" t="s">
+      <c r="AZ2" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="BA2" s="26" t="s">
+      <c r="BA2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="BB2" s="22" t="s">
+      <c r="BB2" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="BC2" s="22" t="s">
+      <c r="BC2" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="BD2" s="22" t="s">
+      <c r="BD2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="BE2" s="26"/>
-      <c r="BF2" s="26"/>
-      <c r="BG2" s="26"/>
-      <c r="BH2" s="26"/>
-      <c r="BI2" s="26"/>
-      <c r="BJ2" s="26"/>
-      <c r="BK2" s="26"/>
-      <c r="BL2" s="26"/>
-      <c r="BM2" s="26"/>
-      <c r="BN2" s="26"/>
-      <c r="BO2" s="27"/>
+      <c r="BE2" s="11"/>
+      <c r="BF2" s="11"/>
+      <c r="BG2" s="11"/>
+      <c r="BH2" s="11"/>
+      <c r="BI2" s="11"/>
+      <c r="BJ2" s="11"/>
+      <c r="BK2" s="11"/>
+      <c r="BL2" s="11"/>
+      <c r="BM2" s="11"/>
+      <c r="BN2" s="11"/>
+      <c r="BO2" s="12"/>
     </row>
     <row r="3" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="26">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="F3" s="1">
+        <v>4.76</v>
+      </c>
+      <c r="G3" s="1">
         <v>4.08</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="1">
         <v>2.83</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="1">
         <v>3.12</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="1">
         <v>1.59</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="1">
         <v>0.39</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="1">
         <v>0.38</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="1">
         <v>0.56999999999999995</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="1">
         <v>0</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="1">
         <v>0</v>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG3" s="1" t="s">
+      <c r="P3" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="R3" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="S3" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="T3" s="1">
+        <v>3</v>
+      </c>
+      <c r="U3" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="V3" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="W3" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="X3" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z3" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD3" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="AG3" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AH3" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AI3" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="AJ3" s="1">
+      <c r="AJ3" s="13">
         <v>730</v>
       </c>
-      <c r="AK3" s="1" t="s">
+      <c r="AK3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AL3" s="4" t="s">
+      <c r="AL3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="AM3" s="4" t="s">
+      <c r="AM3" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="AN3" s="4" t="s">
+      <c r="AN3" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="AO3" s="4" t="s">
+      <c r="AO3" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="AP3" s="4" t="s">
+      <c r="AP3" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="AQ3" s="4" t="s">
+      <c r="AQ3" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="AR3" s="4" t="s">
+      <c r="AR3" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AS3" s="4" t="s">
+      <c r="AS3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AT3" s="4" t="s">
+      <c r="AT3" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="AU3" s="4" t="s">
+      <c r="AU3" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="AV3" s="4" t="s">
+      <c r="AV3" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="AW3" s="1" t="s">
+      <c r="AW3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AX3" s="4" t="s">
+      <c r="AX3" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="AY3" s="4" t="s">
+      <c r="AY3" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AZ3" s="4" t="s">
+      <c r="AZ3" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="BA3" s="4" t="s">
+      <c r="BA3" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="BB3" s="1" t="s">
+      <c r="BB3" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="BC3" s="1" t="s">
+      <c r="BC3" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="BD3" s="1" t="s">
+      <c r="BD3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BE3" s="4"/>
-      <c r="BF3" s="4"/>
-      <c r="BG3" s="4"/>
-      <c r="BH3" s="4"/>
-      <c r="BI3" s="4"/>
-      <c r="BJ3" s="4"/>
-      <c r="BK3" s="4"/>
-      <c r="BL3" s="4"/>
-      <c r="BM3" s="4"/>
-      <c r="BN3" s="4"/>
-      <c r="BO3" s="7"/>
+      <c r="BE3" s="14"/>
+      <c r="BF3" s="14"/>
+      <c r="BG3" s="14"/>
+      <c r="BH3" s="14"/>
+      <c r="BI3" s="14"/>
+      <c r="BJ3" s="14"/>
+      <c r="BK3" s="14"/>
+      <c r="BL3" s="14"/>
+      <c r="BM3" s="14"/>
+      <c r="BN3" s="14"/>
+      <c r="BO3" s="15"/>
     </row>
     <row r="4" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="26">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="1">
         <v>77.44</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="1">
         <v>80.72</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="1">
         <v>100</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="1">
         <v>99.19</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="1">
         <v>98.53</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="1">
         <v>99.89</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="1">
         <v>82.49</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="1">
         <v>91.98</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="1">
         <v>10.42</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="1">
         <v>2.8</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="AG4" s="1" t="s">
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="AG4" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AH4" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AI4" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ4" s="16">
+        <v>1420</v>
+      </c>
+      <c r="AK4" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL4" s="13"/>
+      <c r="AM4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="AN4" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO4" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP4" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ4" s="13"/>
+      <c r="AR4" s="13"/>
+      <c r="AS4" s="13"/>
+      <c r="AT4" s="13"/>
+      <c r="AU4" s="13"/>
+      <c r="AV4" s="13"/>
+      <c r="AW4" s="13"/>
+      <c r="AX4" s="13"/>
+      <c r="AY4" s="13"/>
+      <c r="AZ4" s="13"/>
+      <c r="BA4" s="13"/>
+      <c r="BB4" s="13"/>
+      <c r="BC4" s="13"/>
+      <c r="BD4" s="13"/>
+      <c r="BE4" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="AJ4" s="5">
-        <v>1420</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN4" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO4" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP4" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AQ4" s="1"/>
-      <c r="AR4" s="1"/>
-      <c r="AS4" s="1"/>
-      <c r="AT4" s="1"/>
-      <c r="AU4" s="1"/>
-      <c r="AV4" s="1"/>
-      <c r="AW4" s="1"/>
-      <c r="AX4" s="1"/>
-      <c r="AY4" s="1"/>
-      <c r="AZ4" s="1"/>
-      <c r="BA4" s="1"/>
-      <c r="BB4" s="1"/>
-      <c r="BC4" s="1"/>
-      <c r="BD4" s="1"/>
-      <c r="BE4" s="4" t="s">
+      <c r="BF4" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="BF4" s="4" t="s">
+      <c r="BG4" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="BG4" s="4" t="s">
+      <c r="BH4" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="BI4" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="BH4" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI4" s="4" t="s">
+      <c r="BJ4" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="BJ4" s="4" t="s">
+      <c r="BK4" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="BK4" s="4" t="s">
+      <c r="BL4" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="BL4" s="4" t="s">
+      <c r="BM4" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="BM4" s="4" t="s">
+      <c r="BN4" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="BN4" s="4" t="s">
+      <c r="BO4" s="15" t="s">
         <v>171</v>
-      </c>
-      <c r="BO4" s="7" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="26">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="1">
         <v>93.31</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="1">
         <v>70.3</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="1">
         <v>100</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="1">
         <v>100</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="1">
         <v>100</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="1">
         <v>93.19</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="1">
+        <v>93.37</v>
+      </c>
+      <c r="M5" s="1">
+        <v>63.5</v>
+      </c>
+      <c r="N5" s="1">
         <v>100</v>
       </c>
-      <c r="M5" s="3">
-        <v>63.5</v>
-      </c>
-      <c r="N5" s="3">
+      <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="O5" s="3">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG5" s="1" t="s">
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG5" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="AH5" s="1" t="s">
+      <c r="AH5" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AI5" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AJ5" s="5">
+      <c r="AI5" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ5" s="16">
         <v>1720</v>
       </c>
-      <c r="AK5" s="1" t="s">
+      <c r="AK5" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="4" t="s">
+      <c r="AL5" s="13"/>
+      <c r="AM5" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="AN5" s="4" t="s">
+      <c r="AN5" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AO5" s="4" t="s">
+      <c r="AO5" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AP5" s="4" t="s">
+      <c r="AP5" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="AQ5" s="1"/>
-      <c r="AR5" s="1"/>
-      <c r="AS5" s="1"/>
-      <c r="AT5" s="1"/>
-      <c r="AU5" s="1"/>
-      <c r="AV5" s="1"/>
-      <c r="AW5" s="1"/>
-      <c r="AX5" s="1"/>
-      <c r="AY5" s="1"/>
-      <c r="AZ5" s="1"/>
-      <c r="BA5" s="1"/>
-      <c r="BB5" s="1"/>
-      <c r="BC5" s="1"/>
-      <c r="BD5" s="1"/>
-      <c r="BE5" s="4" t="s">
+      <c r="AQ5" s="13"/>
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="13"/>
+      <c r="AT5" s="13"/>
+      <c r="AU5" s="13"/>
+      <c r="AV5" s="13"/>
+      <c r="AW5" s="13"/>
+      <c r="AX5" s="13"/>
+      <c r="AY5" s="13"/>
+      <c r="AZ5" s="13"/>
+      <c r="BA5" s="13"/>
+      <c r="BB5" s="13"/>
+      <c r="BC5" s="13"/>
+      <c r="BD5" s="13"/>
+      <c r="BE5" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF5" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="BF5" s="4" t="s">
+      <c r="BG5" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="BG5" s="4" t="s">
+      <c r="BH5" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="BH5" s="4" t="s">
+      <c r="BI5" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="BI5" s="4" t="s">
+      <c r="BJ5" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="BJ5" s="4" t="s">
+      <c r="BK5" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="BK5" s="4" t="s">
+      <c r="BL5" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="BL5" s="4" t="s">
+      <c r="BM5" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="BM5" s="4" t="s">
+      <c r="BN5" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="BN5" s="4" t="s">
+      <c r="BO5" s="15" t="s">
         <v>160</v>
-      </c>
-      <c r="BO5" s="7" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="26">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="1">
         <v>100</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="1">
         <v>33.43</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="1">
         <v>100</v>
       </c>
-      <c r="I6" s="3">
-        <v>16.23</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="I6" s="1">
+        <v>64.92</v>
+      </c>
+      <c r="J6" s="1">
         <v>100</v>
       </c>
-      <c r="K6" s="3">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="K6" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="L6" s="1">
         <v>100</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="1">
         <v>12.53</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="1">
+        <v>100</v>
+      </c>
+      <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="O6" s="3">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="AG6" s="1" t="s">
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG6" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AH6" s="1" t="s">
+      <c r="AH6" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AI6" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AJ6" s="5">
+      <c r="AI6" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ6" s="16">
         <v>1896</v>
       </c>
-      <c r="AK6" s="1" t="s">
+      <c r="AK6" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AL6" s="1"/>
-      <c r="AM6" s="4" t="s">
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="AN6" s="4" t="s">
+      <c r="AN6" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="AO6" s="4" t="s">
+      <c r="AO6" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="AP6" s="4" t="s">
+      <c r="AP6" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="AQ6" s="1"/>
-      <c r="AR6" s="1"/>
-      <c r="AS6" s="1"/>
-      <c r="AT6" s="1"/>
-      <c r="AU6" s="1"/>
-      <c r="AV6" s="1"/>
-      <c r="AW6" s="1"/>
-      <c r="AX6" s="1"/>
-      <c r="AY6" s="1"/>
-      <c r="AZ6" s="1"/>
-      <c r="BA6" s="1"/>
-      <c r="BB6" s="1"/>
-      <c r="BC6" s="1"/>
-      <c r="BD6" s="1"/>
-      <c r="BE6" s="4">
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="13"/>
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="13"/>
+      <c r="AX6" s="13"/>
+      <c r="AY6" s="13"/>
+      <c r="AZ6" s="13"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="13"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="13"/>
+      <c r="BE6" s="14">
         <v>10</v>
       </c>
-      <c r="BF6" s="4">
+      <c r="BF6" s="14">
         <v>46.85</v>
       </c>
-      <c r="BG6" s="4">
+      <c r="BG6" s="14">
         <v>54.5</v>
       </c>
-      <c r="BH6" s="4">
+      <c r="BH6" s="14">
         <v>2</v>
       </c>
-      <c r="BI6" s="4" t="s">
+      <c r="BI6" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="BJ6" s="14">
+        <v>11.5</v>
+      </c>
+      <c r="BK6" s="14">
+        <v>50</v>
+      </c>
+      <c r="BL6" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="BJ6" s="4">
-        <v>11.5</v>
-      </c>
-      <c r="BK6" s="4">
-        <v>50</v>
-      </c>
-      <c r="BL6" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="BM6" s="4">
+      <c r="BM6" s="14">
         <v>31.48</v>
       </c>
-      <c r="BN6" s="4">
+      <c r="BN6" s="14">
         <v>21.193000000000001</v>
       </c>
-      <c r="BO6" s="7">
+      <c r="BO6" s="15">
         <v>8944</v>
       </c>
     </row>
     <row r="7" spans="1:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="27">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="F7" s="11">
-        <v>49.66</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="F7" s="2">
         <v>49.7</v>
       </c>
-      <c r="H7" s="12">
+      <c r="G7" s="2">
+        <v>49.7</v>
+      </c>
+      <c r="H7" s="2">
+        <v>72.69</v>
+      </c>
+      <c r="I7" s="2">
+        <v>58.9</v>
+      </c>
+      <c r="J7" s="2">
+        <v>54.53</v>
+      </c>
+      <c r="K7" s="2">
+        <v>55.68</v>
+      </c>
+      <c r="L7" s="2">
+        <v>51.26</v>
+      </c>
+      <c r="M7" s="2">
+        <v>49.9</v>
+      </c>
+      <c r="N7" s="2">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="O7" s="2">
         <v>0.59</v>
       </c>
-      <c r="I7" s="11">
-        <v>0.59</v>
-      </c>
-      <c r="J7" s="12">
-        <v>15.69</v>
-      </c>
-      <c r="K7" s="11">
-        <v>15.69</v>
-      </c>
-      <c r="L7" s="12">
-        <v>33.409999999999997</v>
-      </c>
-      <c r="M7" s="11">
-        <v>33.409999999999997</v>
-      </c>
-      <c r="N7" s="12">
-        <v>0.01</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="11"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG7" s="9" t="s">
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2"/>
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="AG7" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="AH7" s="9" t="s">
+      <c r="AH7" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="AI7" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="AJ7" s="13">
+      <c r="AI7" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ7" s="18">
         <v>1750</v>
       </c>
-      <c r="AK7" s="9" t="s">
+      <c r="AK7" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="AL7" s="9"/>
-      <c r="AM7" s="14" t="s">
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AN7" s="14" t="s">
+      <c r="AN7" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="AO7" s="14" t="s">
+      <c r="AO7" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="AP7" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="AQ7" s="9"/>
-      <c r="AR7" s="9"/>
-      <c r="AS7" s="9"/>
-      <c r="AT7" s="9"/>
-      <c r="AU7" s="9"/>
-      <c r="AV7" s="9"/>
-      <c r="AW7" s="9"/>
-      <c r="AX7" s="9"/>
-      <c r="AY7" s="9"/>
-      <c r="AZ7" s="9"/>
-      <c r="BA7" s="9"/>
-      <c r="BB7" s="9"/>
-      <c r="BC7" s="9"/>
-      <c r="BD7" s="9"/>
-      <c r="BE7" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="BF7" s="14" t="s">
+      <c r="AP7" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="AQ7" s="17"/>
+      <c r="AR7" s="17"/>
+      <c r="AS7" s="17"/>
+      <c r="AT7" s="17"/>
+      <c r="AU7" s="17"/>
+      <c r="AV7" s="17"/>
+      <c r="AW7" s="17"/>
+      <c r="AX7" s="17"/>
+      <c r="AY7" s="17"/>
+      <c r="AZ7" s="17"/>
+      <c r="BA7" s="17"/>
+      <c r="BB7" s="17"/>
+      <c r="BC7" s="17"/>
+      <c r="BD7" s="17"/>
+      <c r="BE7" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="BG7" s="14" t="s">
+      <c r="BF7" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="BH7" s="14" t="s">
+      <c r="BG7" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="BI7" s="14" t="s">
+      <c r="BH7" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="BJ7" s="14" t="s">
+      <c r="BI7" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="BK7" s="14" t="s">
+      <c r="BJ7" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="BL7" s="14" t="s">
+      <c r="BK7" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="BM7" s="14" t="s">
+      <c r="BL7" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="BN7" s="14" t="s">
+      <c r="BM7" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="BO7" s="15" t="s">
+      <c r="BN7" s="19" t="s">
         <v>173</v>
+      </c>
+      <c r="BO7" s="20" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\CPEL_APP_V1\cartera-cpel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\proyectos_cpel-claude-code-improvement-analysis-0rbe6x 2\proyectos_cpel-claude-code-improvement-analysis-0rbe6x\cartera-cpel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AEE5E2-6E0F-4D00-9CA8-C703BC0F25A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8634B29E-71D4-4818-93A2-4726F296CF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -604,35 +604,6 @@
     <t>240</t>
   </si>
   <si>
-    <t>•	11 y 12 sept: Arribaron 15 contenedores con 15 Centros de Transformación (30 inversores), al almacén temporal del Contratista en Puerto Peñasco. Con este suministro se tiene un total acumulado de 33 CT's de 38 totales en Sitio (86.84%).
-•	11 al 15-sep: Arribaron 17 contenedores con 12,064 Hincas (parte del Sistema de Seguimiento), en la plataforma provisional en sitio. Con este suministro se tiene un total acumulado de 39,649 hincas de 84,182 en Sitio (47.09%).
-•	Continúan actividades de hincado de perfiles correspondientes al Sistema de Seguimiento, en los cuadrantes CT-02 y CT-03, Zona Sur del Polígono, así como actividades de replanteo, conformación de plataformas en Centro de Interconexión con un avance del 70%, así como trabajos de conformación de plataforma en Subestación de Maniobras Puerto Peñasco 400 kV con un avance del 10%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Obra civil: Continúan los trabajos limpieza del terreno en la Zona Norte (subzona 4) del polígono de la CFV, con un avance de 73.12 Ha de 465.68 Ha (15.70%). Continúan trabajos de nivelación de terreno con un avance del 40.00 Ha de 465.68 Ha (8.58%).
-•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte (subzonas 1, 2, 3, 4 y 5). </t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	En proceso de formalización del Primer Convenio Modificatorio del Contrato F/1320/001/2022.
-•	Se encuentra en elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
-•	Obra Civil: Continúa la construcción de la Pantalla Impermeable del eje principal, Empaque de los Tubos de Aspiración de las Unidades de Casa de Máquinas, así como colocación de Hardfill en Muro de Cierre Margen Izquierda y Toma Ecológica; de igual forma la construcción de la cimentación del Cimacio.
-•	Obra Electromecánica: Continúa el montaje de los Tubos de Aspiración y Columnas fijas de las 3 Unidades; así como la Nariz de Bulbo de la U1, en Casa de Máquinas. En Playa de Montaje se continúa el ensamble del Estator de las 3 Unidades y el Rotor de la U1. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	22-sep-26: El Contratista deberá disponer y emplear de todos los recursos materiales y humanos para poder concluir el Proyecto en la fecha programada conforme al Convenio 7. La Contratante estará atenta en detectar y señalar las desviaciones al programa para realizar las acciones necesarias para la recuperación de los posibles retrasos, principalmente en las Pruebas de Puesta y Servicio de las dos Unidades Generadoras, y Aceptación de las mismas.
-•	El Contratista debe incrementar la presencia de personal y darles continuidad a los trabajos en el turno nocturno.
-•	La Contratante y Contratistas se están coordinando para dar atención a los temas relacionados con CENACE y Transmisión de CFE para las Pruebas de Puesta en Servicio y Aceptación de las dos Unidades Generadoras. </t>
-  </si>
-  <si>
-    <t>•	Contrato de Obra Electromecánica Principal (Siemens Energy): Proceso de Terminación Anticipada.
-•	Contrato de Auxiliares de Casa de Maquinas (COSEGO Ingeniería): En conciliación de Convenio Modificatorio para dar vigencia al Contrato y realizar el pago del Hito No. 03 (suministro).
-•	Obra Civil: Suspendidas, a cargo del Gobierno del Estado de Sinaloa. Se realizan reuniones entre la SOP y la CFE para la entrega recepción de las Obras Civiles. Se requiere intervención del área interinstitucional de la CFE para agilizar el proceso de cierre administrativo de los contratos civiles por parte del Gobierno de Sinaloa.</t>
-  </si>
-  <si>
-    <t>•	Obra Civil: La CFE y la Secretaría de Obras Públicas del Estado de Sinaloa atienden los compromisos para la entrega de las obras civiles y están a la espera de que la dependencia confirme la fecha para el cierre administrativo y el finiquito de los contratos.
-•	Obra Electromecánica: Conciliar las Razones Fundadas y Explicitas y celebrar con el Contratista Andritz el Primer Convenio Modificatorio del Contrato No. F/10670-021/2024 de la Obra Electromecánica.</t>
-  </si>
-  <si>
     <t>30/12/2028</t>
   </si>
   <si>
@@ -691,6 +662,43 @@
   </si>
   <si>
     <t>Colocación de Órdenes de Compra de equipos electromecánicos del Parque Fotovoltaico</t>
+  </si>
+  <si>
+    <t>•	25-sep: El Fideicomiso realizó el pago del H5 (5%) y el H9 (5%) por un monto total del $29.4 MDD.
+•	26-sep: El Contratista remitió carta invitación a Pruebas FAT de transformador de potencia.
+•	29-sep: Suministro en sitio de 2,688 hincas (parte del Sistema de Seguimiento), alcanzando un acumulado de 52,956 hincas de 84,182 programadas en sitio (62.90% de avance).
+•	Obra electromecánica: Continúan actividades de hincado de perfiles correspondientes al Sistema de Seguimiento en los cuadrantes CT-01, CT-02, CT-03, CT-04 y CT-05 Zona Sur del Polígono. 
+•	Obra civil: Continúan actividades de replanteo, conformación de plataformas en Centro de Interconexión con un avance del 97%, así como trabajos de conformación de plataforma en Subestación de Maniobras Puerto Peñasco 400 kV con un avance del 65%.</t>
+  </si>
+  <si>
+    <t>•	25 al 28 sep: Trabajos de limpieza y nivelación del terreno para el patio de maniobras de S.E. Cucapah Bco. 3. Asimismo, el 28 de septiembre iniciaron los trabajos de conformación de la plataforma correspondiente.
+•	26-sep: El Contratista remitió carta invitación a Pruebas FAT de cuchillas desconectadoras tripolares CM &amp; CMC.
+•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte (subzonas 1, 2, 3, 4 y 5).
+•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Norte (subzona 4) del polígono de la CFV, con un avance de 146.68 Ha de 465.68 Ha (31.49%). Continúan trabajos de nivelación de terreno con un avance de 43.43 Ha de 465.68 Ha (9.32%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Se continua con la elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
+•	25-sep: El Fideicomiso y el Proveedor GE formalizaron el Primer Convenio Modificatorio al Contrato de Adquisiciones de Bienes y prestaciones No. F/1320/001/2022. 
+•	28 y 29-sep: Traslado de los 4 segmentos del Cono Fijo U1 desde el Almacén 205 MI a la plataforma 183 (zona de obras) para iniciar su preensamble. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para octubre y noviembre de 2026.
+•	En proceso de conciliación los avances parciales de los hitos de suministro de las unidades U1 y U2 (H4 e H5).
+•	Se requiere reforzar los frentes de obra electromecánica y puesta en servicio, así como mantener la continuidad de los trabajos en turno nocturno para mitigar riesgos al programa de ejecución. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Se está gestionando la entrega-recepción de las obras civiles y el cierre del Convenio de Colaboración entre la CFE y el Estado de Sinaloa.
+•	En proceso de conciliación la Terminación Anticipada del Contrato de Obra Electromecánica Principal con SIEMES.
+•	Se esta conciliando el Convenio Modificatorio con el Contratista COSEGO.
+•	Se ha analizado y está pendiente definir si es conveniente realizar la Terminación Anticipada de los Contratos Electromecánicos Auxiliares, dada la Terminación del Contrato de Obra Electromecánica Principal.
+•	Definición del mecanismo de financiamiento para la contratación y culminación de las obras civiles y electromecánicas.
+•	Se ha integrado el paquete técnico de la obra civil y está pendiente el de la electromecánica restante de ejecutar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Continúa pendiente la contratación de las obras civiles para la conclusión del proyecto.
+•	Se está gestionando la entrega recepción de las obras civiles, así como del finiquito los contratos a cargo de la SOP.
+•	En proceso de gestión, la formalización del Primer Convenio Modificatorio del Contrato No. F/10670-021/2024 de la obra electromecánica con Andritz.
+•	Las condiciones de inseguridad en la zona de influencia del proyecto continúan representando un factor de riesgo para su ejecución. </t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1037,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1076,6 +1084,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1663,28 +1673,28 @@
         <v>70</v>
       </c>
       <c r="F2" s="7">
-        <v>30.76</v>
+        <v>31.46</v>
       </c>
       <c r="G2" s="7">
-        <v>27.79</v>
+        <v>28.48</v>
       </c>
       <c r="H2" s="7">
-        <v>6.05</v>
+        <v>6.18</v>
       </c>
       <c r="I2" s="7">
-        <v>5.29</v>
+        <v>5.48</v>
       </c>
       <c r="J2" s="7">
-        <v>16.350000000000001</v>
+        <v>16.59</v>
       </c>
       <c r="K2" s="7">
-        <v>16.34</v>
+        <v>16.57</v>
       </c>
       <c r="L2" s="7">
-        <v>8.36</v>
+        <v>8.69</v>
       </c>
       <c r="M2" s="7">
-        <v>6.16</v>
+        <v>6.43</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
@@ -1696,52 +1706,52 @@
         <v>6</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="R2" s="32" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="T2" s="7">
         <v>5</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="X2" s="7">
         <v>9</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="Z2" s="8" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AB2" s="7">
         <v>8</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AD2" s="8" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AE2" s="28" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AF2" s="9" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="AG2" s="10" t="s">
         <v>71</v>
@@ -1844,10 +1854,10 @@
         <v>94</v>
       </c>
       <c r="F3" s="1">
-        <v>4.76</v>
+        <v>5.26</v>
       </c>
       <c r="G3" s="1">
-        <v>4.08</v>
+        <v>7.59</v>
       </c>
       <c r="H3" s="1">
         <v>2.83</v>
@@ -1856,13 +1866,13 @@
         <v>3.12</v>
       </c>
       <c r="J3" s="1">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="K3" s="1">
-        <v>0.39</v>
+        <v>3.9</v>
       </c>
       <c r="L3" s="1">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="M3" s="1">
         <v>0.56999999999999995</v>
@@ -1877,52 +1887,52 @@
         <v>2</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="S3" s="31" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="T3" s="1">
         <v>3</v>
       </c>
       <c r="U3" s="30" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V3" s="29" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="W3" s="31" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="X3" s="1">
         <v>5</v>
       </c>
       <c r="Y3" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z3" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="Z3" s="29" t="s">
-        <v>205</v>
-      </c>
       <c r="AA3" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="AB3" s="1">
         <v>4</v>
       </c>
       <c r="AC3" s="30" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AD3" s="29" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>184</v>
+        <v>202</v>
+      </c>
+      <c r="AF3" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="AG3" s="13" t="s">
         <v>71</v>
@@ -2025,34 +2035,34 @@
         <v>112</v>
       </c>
       <c r="F4" s="1">
-        <v>77.44</v>
+        <v>78.510000000000005</v>
       </c>
       <c r="G4" s="1">
-        <v>80.72</v>
+        <v>81.63</v>
       </c>
       <c r="H4" s="1">
         <v>100</v>
       </c>
       <c r="I4" s="1">
-        <v>99.19</v>
+        <v>99.39</v>
       </c>
       <c r="J4" s="1">
-        <v>98.53</v>
+        <v>99.74</v>
       </c>
       <c r="K4" s="1">
-        <v>99.89</v>
+        <v>99.93</v>
       </c>
       <c r="L4" s="1">
-        <v>82.49</v>
+        <v>82.58</v>
       </c>
       <c r="M4" s="1">
-        <v>91.98</v>
+        <v>92.32</v>
       </c>
       <c r="N4" s="1">
-        <v>10.42</v>
+        <v>13.49</v>
       </c>
       <c r="O4" s="1">
-        <v>2.8</v>
+        <v>4.12</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -2070,8 +2080,8 @@
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
-      <c r="AF4" s="1" t="s">
-        <v>186</v>
+      <c r="AF4" s="34" t="s">
+        <v>206</v>
       </c>
       <c r="AG4" s="13" t="s">
         <v>113</v>
@@ -2169,7 +2179,7 @@
         <v>93.31</v>
       </c>
       <c r="G5" s="1">
-        <v>70.3</v>
+        <v>70.02</v>
       </c>
       <c r="H5" s="1">
         <v>100</v>
@@ -2190,7 +2200,7 @@
         <v>63.5</v>
       </c>
       <c r="N5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -2211,8 +2221,8 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
-      <c r="AF5" s="1" t="s">
-        <v>187</v>
+      <c r="AF5" s="34" t="s">
+        <v>207</v>
       </c>
       <c r="AG5" s="13" t="s">
         <v>122</v>
@@ -2310,13 +2320,13 @@
         <v>100</v>
       </c>
       <c r="G6" s="1">
-        <v>33.43</v>
+        <v>33.64</v>
       </c>
       <c r="H6" s="1">
         <v>100</v>
       </c>
       <c r="I6" s="1">
-        <v>64.92</v>
+        <v>65</v>
       </c>
       <c r="J6" s="1">
         <v>100</v>
@@ -2352,8 +2362,8 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
-      <c r="AF6" s="1" t="s">
-        <v>188</v>
+      <c r="AF6" s="34" t="s">
+        <v>208</v>
       </c>
       <c r="AG6" s="13" t="s">
         <v>132</v>
@@ -2448,34 +2458,34 @@
         <v>142</v>
       </c>
       <c r="F7" s="2">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="G7" s="2">
-        <v>49.7</v>
+        <v>49.3</v>
       </c>
       <c r="H7" s="2">
-        <v>72.69</v>
+        <v>75.77</v>
       </c>
       <c r="I7" s="2">
-        <v>58.9</v>
+        <v>59.09</v>
       </c>
       <c r="J7" s="2">
-        <v>54.53</v>
+        <v>54.33</v>
       </c>
       <c r="K7" s="2">
-        <v>55.68</v>
+        <v>54.41</v>
       </c>
       <c r="L7" s="2">
-        <v>51.26</v>
+        <v>45.35</v>
       </c>
       <c r="M7" s="2">
-        <v>49.9</v>
+        <v>46.36</v>
       </c>
       <c r="N7" s="2">
-        <v>35.479999999999997</v>
+        <v>14.61</v>
       </c>
       <c r="O7" s="2">
-        <v>0.59</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
@@ -2493,8 +2503,8 @@
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
-      <c r="AF7" s="2" t="s">
-        <v>185</v>
+      <c r="AF7" s="35" t="s">
+        <v>205</v>
       </c>
       <c r="AG7" s="17" t="s">
         <v>143</v>
@@ -2522,7 +2532,7 @@
         <v>147</v>
       </c>
       <c r="AP7" s="19" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="AQ7" s="17"/>
       <c r="AR7" s="17"/>

--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\proyectos_cpel-claude-code-improvement-analysis-0rbe6x 2\proyectos_cpel-claude-code-improvement-analysis-0rbe6x\cartera-cpel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8634B29E-71D4-4818-93A2-4726F296CF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BE42CB-062F-4470-B75C-0F748CD113F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -664,41 +664,38 @@
     <t>Colocación de Órdenes de Compra de equipos electromecánicos del Parque Fotovoltaico</t>
   </si>
   <si>
-    <t>•	25-sep: El Fideicomiso realizó el pago del H5 (5%) y el H9 (5%) por un monto total del $29.4 MDD.
-•	26-sep: El Contratista remitió carta invitación a Pruebas FAT de transformador de potencia.
-•	29-sep: Suministro en sitio de 2,688 hincas (parte del Sistema de Seguimiento), alcanzando un acumulado de 52,956 hincas de 84,182 programadas en sitio (62.90% de avance).
-•	Obra electromecánica: Continúan actividades de hincado de perfiles correspondientes al Sistema de Seguimiento en los cuadrantes CT-01, CT-02, CT-03, CT-04 y CT-05 Zona Sur del Polígono. 
-•	Obra civil: Continúan actividades de replanteo, conformación de plataformas en Centro de Interconexión con un avance del 97%, así como trabajos de conformación de plataforma en Subestación de Maniobras Puerto Peñasco 400 kV con un avance del 65%.</t>
-  </si>
-  <si>
-    <t>•	25 al 28 sep: Trabajos de limpieza y nivelación del terreno para el patio de maniobras de S.E. Cucapah Bco. 3. Asimismo, el 28 de septiembre iniciaron los trabajos de conformación de la plataforma correspondiente.
-•	26-sep: El Contratista remitió carta invitación a Pruebas FAT de cuchillas desconectadoras tripolares CM &amp; CMC.
-•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte (subzonas 1, 2, 3, 4 y 5).
-•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Norte (subzona 4) del polígono de la CFV, con un avance de 146.68 Ha de 465.68 Ha (31.49%). Continúan trabajos de nivelación de terreno con un avance de 43.43 Ha de 465.68 Ha (9.32%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Se continua con la elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
-•	25-sep: El Fideicomiso y el Proveedor GE formalizaron el Primer Convenio Modificatorio al Contrato de Adquisiciones de Bienes y prestaciones No. F/1320/001/2022. 
-•	28 y 29-sep: Traslado de los 4 segmentos del Cono Fijo U1 desde el Almacén 205 MI a la plataforma 183 (zona de obras) para iniciar su preensamble. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para octubre y noviembre de 2026.
-•	En proceso de conciliación los avances parciales de los hitos de suministro de las unidades U1 y U2 (H4 e H5).
-•	Se requiere reforzar los frentes de obra electromecánica y puesta en servicio, así como mantener la continuidad de los trabajos en turno nocturno para mitigar riesgos al programa de ejecución. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Se está gestionando la entrega-recepción de las obras civiles y el cierre del Convenio de Colaboración entre la CFE y el Estado de Sinaloa.
-•	En proceso de conciliación la Terminación Anticipada del Contrato de Obra Electromecánica Principal con SIEMES.
-•	Se esta conciliando el Convenio Modificatorio con el Contratista COSEGO.
-•	Se ha analizado y está pendiente definir si es conveniente realizar la Terminación Anticipada de los Contratos Electromecánicos Auxiliares, dada la Terminación del Contrato de Obra Electromecánica Principal.
-•	Definición del mecanismo de financiamiento para la contratación y culminación de las obras civiles y electromecánicas.
-•	Se ha integrado el paquete técnico de la obra civil y está pendiente el de la electromecánica restante de ejecutar. </t>
+    <t>•	Del 29-sep-26 al 01-oct-26: Arribaron 14 contenedores con 9,135 Hincas (parte del Sistema de Seguimiento), en la plataforma provisional en sitio, con el cual se tiene un total acumulado de 59,403 hincas de 84,182 en Sitio (70.56%). 
+•	Del 03-oct al 06 de oct: Arribaron 45 contenedores con 31,500 módulos fotovoltaicos, se tienen en sitio 50,400 piezas de 562,890 totales en la plataforma provisional en Sitio (8.95%).
+•	07-oct: El Contratista emitió entregables correspondientes al Cumplimiento del Hito No. 7 Terminación de la Obra civil de las Plataformas de Centro de Interconexión y SE Maniobras CFV Puerto Peñasco 400 kV, en revisión por CFE.
+•	Obra electromecánica: Continúan actividades de hincado de perfiles correspondientes al Sistema de Seguimiento en los cuadrantes CT-01 al CT-07 en Zona Sur del polígono de la CFV con un avance acumulado de 11,164 de 84,182 Hincas colocadas (13.26%).
+•	Obra civil: Concluye conformación de plataforma en Subestación Maniobras Puerto Peñasco 400 kV (Capa 15 de 15 equivalente al 100% de avance).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte (subzonas 1, 2, 3, 4 y 5).
+•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Norte (subzona 4, 3, 2 y 1) del polígono de la CFV, con un avance de 158.42 Ha de 465.68 Ha (34.01%). Continúan trabajos de nivelación de terreno (subzona 4 y 3) con un avance de 53.77 Ha de 465.68 Ha (11.54%). El 05-oct iniciaron los trabajos de limpieza del terreno en subzona 5 de la Zona Norte del polígono de la CFV. </t>
+  </si>
+  <si>
+    <t>•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para octubre y noviembre de 2026.
+•	En proceso de conciliación los avances parciales de los hitos (H4, H5, H7 y H8) correspondientes a los suministros y montaje de las unidades.
+•	Se requiere reforzar los frentes de obra electromecánica y puesta en servicio, así como mantener la continuidad de los trabajos en turno nocturno para mitigar riesgos al programa de ejecución.</t>
+  </si>
+  <si>
+    <t>•	Se está gestionando la entrega-recepción de las obras civiles y el cierre del Convenio de Colaboración entre la CFE y el Estado de Sinaloa.
+•	En proceso de conciliación la Terminación Anticipada del Contrato de Obra Electromecánica Principal con Siemens Energy.
+•	El 01-oct se formalizó el primer Convenio Modificatorio con el Contratista COSEGO. En trámite el pago del Hito No. 03.
+•	Pendiente definir por el Fideicomiso la conveniencia de realizar la Terminación Anticipada de los Contratos Electromecánicos Auxiliares, derivado de la Terminación del Contrato de Obra Electromecánica Principal.
+•	Pendiente definir del mecanismo de financiamiento para la contratación y culminación de las obras civiles y electromecánicas.</t>
   </si>
   <si>
     <t xml:space="preserve">•	Continúa pendiente la contratación de las obras civiles para la conclusión del proyecto.
 •	Se está gestionando la entrega recepción de las obras civiles, así como del finiquito los contratos a cargo de la SOP.
 •	En proceso de gestión, la formalización del Primer Convenio Modificatorio del Contrato No. F/10670-021/2024 de la obra electromecánica con Andritz.
-•	Las condiciones de inseguridad en la zona de influencia del proyecto continúan representando un factor de riesgo para su ejecución. </t>
+•	Se continua con el desarrollo y revisión de la Ingeniería correspondiente al Contrato Electromecánico. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Se continua con la elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
+•	05-oct: Inicia el ensamble de las 4 secciones que conforman el Cono Fijo U1 en la plataforma 183 (zona de obras).
+•	06-oct:  Se realizó la colocación de concreto correspondiente a los segundos colados de la losa de la U3 del Desfogue (208 m³) y a la segunda alzada de la Pila 4 de la Obra de Toma (180 m³). </t>
   </si>
 </sst>
 </file>
@@ -1673,28 +1670,28 @@
         <v>70</v>
       </c>
       <c r="F2" s="7">
-        <v>31.46</v>
+        <v>32.54</v>
       </c>
       <c r="G2" s="7">
-        <v>28.48</v>
+        <v>29.59</v>
       </c>
       <c r="H2" s="7">
-        <v>6.18</v>
+        <v>6.27</v>
       </c>
       <c r="I2" s="7">
-        <v>5.48</v>
+        <v>6.12</v>
       </c>
       <c r="J2" s="7">
-        <v>16.59</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="K2" s="7">
-        <v>16.57</v>
+        <v>16.89</v>
       </c>
       <c r="L2" s="7">
-        <v>8.69</v>
+        <v>9.19</v>
       </c>
       <c r="M2" s="7">
-        <v>6.43</v>
+        <v>6.58</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
@@ -1854,10 +1851,10 @@
         <v>94</v>
       </c>
       <c r="F3" s="1">
-        <v>5.26</v>
+        <v>5.9</v>
       </c>
       <c r="G3" s="1">
-        <v>7.59</v>
+        <v>7.68</v>
       </c>
       <c r="H3" s="1">
         <v>2.83</v>
@@ -1866,16 +1863,16 @@
         <v>3.12</v>
       </c>
       <c r="J3" s="1">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="K3" s="1">
-        <v>3.9</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="L3" s="1">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="M3" s="1">
-        <v>0.56999999999999995</v>
+        <v>0.5</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -2035,34 +2032,34 @@
         <v>112</v>
       </c>
       <c r="F4" s="1">
-        <v>78.510000000000005</v>
+        <v>79.209999999999994</v>
       </c>
       <c r="G4" s="1">
-        <v>81.63</v>
+        <v>83.22</v>
       </c>
       <c r="H4" s="1">
         <v>100</v>
       </c>
       <c r="I4" s="1">
-        <v>99.39</v>
+        <v>99.37</v>
       </c>
       <c r="J4" s="1">
-        <v>99.74</v>
+        <v>100</v>
       </c>
       <c r="K4" s="1">
         <v>99.93</v>
       </c>
       <c r="L4" s="1">
-        <v>82.58</v>
+        <v>82.71</v>
       </c>
       <c r="M4" s="1">
-        <v>92.32</v>
+        <v>92.36</v>
       </c>
       <c r="N4" s="1">
-        <v>13.49</v>
+        <v>14.89</v>
       </c>
       <c r="O4" s="1">
-        <v>4.12</v>
+        <v>9.58</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -2081,7 +2078,7 @@
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG4" s="13" t="s">
         <v>113</v>
@@ -2222,7 +2219,7 @@
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG5" s="13" t="s">
         <v>122</v>
@@ -2320,13 +2317,13 @@
         <v>100</v>
       </c>
       <c r="G6" s="1">
-        <v>33.64</v>
+        <v>33.67</v>
       </c>
       <c r="H6" s="1">
         <v>100</v>
       </c>
       <c r="I6" s="1">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J6" s="1">
         <v>100</v>
@@ -2363,7 +2360,7 @@
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
       <c r="AF6" s="34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG6" s="13" t="s">
         <v>132</v>
@@ -2458,31 +2455,31 @@
         <v>142</v>
       </c>
       <c r="F7" s="2">
-        <v>49.2</v>
+        <v>51.68</v>
       </c>
       <c r="G7" s="2">
         <v>49.3</v>
       </c>
       <c r="H7" s="2">
-        <v>75.77</v>
+        <v>79.56</v>
       </c>
       <c r="I7" s="2">
         <v>59.09</v>
       </c>
       <c r="J7" s="2">
-        <v>54.33</v>
+        <v>56.6</v>
       </c>
       <c r="K7" s="2">
         <v>54.41</v>
       </c>
       <c r="L7" s="2">
-        <v>45.35</v>
+        <v>47.71</v>
       </c>
       <c r="M7" s="2">
-        <v>46.36</v>
+        <v>46.35</v>
       </c>
       <c r="N7" s="2">
-        <v>14.61</v>
+        <v>18.07</v>
       </c>
       <c r="O7" s="2">
         <v>0.56000000000000005</v>
@@ -2504,7 +2501,7 @@
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
       <c r="AF7" s="35" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG7" s="17" t="s">
         <v>143</v>

--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BE42CB-062F-4470-B75C-0F748CD113F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5836CCC-3146-4BD1-A74A-122DB31797DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -664,38 +664,40 @@
     <t>Colocación de Órdenes de Compra de equipos electromecánicos del Parque Fotovoltaico</t>
   </si>
   <si>
-    <t>•	Del 29-sep-26 al 01-oct-26: Arribaron 14 contenedores con 9,135 Hincas (parte del Sistema de Seguimiento), en la plataforma provisional en sitio, con el cual se tiene un total acumulado de 59,403 hincas de 84,182 en Sitio (70.56%). 
-•	Del 03-oct al 06 de oct: Arribaron 45 contenedores con 31,500 módulos fotovoltaicos, se tienen en sitio 50,400 piezas de 562,890 totales en la plataforma provisional en Sitio (8.95%).
-•	07-oct: El Contratista emitió entregables correspondientes al Cumplimiento del Hito No. 7 Terminación de la Obra civil de las Plataformas de Centro de Interconexión y SE Maniobras CFV Puerto Peñasco 400 kV, en revisión por CFE.
-•	Obra electromecánica: Continúan actividades de hincado de perfiles correspondientes al Sistema de Seguimiento en los cuadrantes CT-01 al CT-07 en Zona Sur del polígono de la CFV con un avance acumulado de 11,164 de 84,182 Hincas colocadas (13.26%).
-•	Obra civil: Concluye conformación de plataforma en Subestación Maniobras Puerto Peñasco 400 kV (Capa 15 de 15 equivalente al 100% de avance).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte (subzonas 1, 2, 3, 4 y 5).
-•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Norte (subzona 4, 3, 2 y 1) del polígono de la CFV, con un avance de 158.42 Ha de 465.68 Ha (34.01%). Continúan trabajos de nivelación de terreno (subzona 4 y 3) con un avance de 53.77 Ha de 465.68 Ha (11.54%). El 05-oct iniciaron los trabajos de limpieza del terreno en subzona 5 de la Zona Norte del polígono de la CFV. </t>
-  </si>
-  <si>
-    <t>•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para octubre y noviembre de 2026.
-•	En proceso de conciliación los avances parciales de los hitos (H4, H5, H7 y H8) correspondientes a los suministros y montaje de las unidades.
-•	Se requiere reforzar los frentes de obra electromecánica y puesta en servicio, así como mantener la continuidad de los trabajos en turno nocturno para mitigar riesgos al programa de ejecución.</t>
-  </si>
-  <si>
-    <t>•	Se está gestionando la entrega-recepción de las obras civiles y el cierre del Convenio de Colaboración entre la CFE y el Estado de Sinaloa.
-•	En proceso de conciliación la Terminación Anticipada del Contrato de Obra Electromecánica Principal con Siemens Energy.
-•	El 01-oct se formalizó el primer Convenio Modificatorio con el Contratista COSEGO. En trámite el pago del Hito No. 03.
-•	Pendiente definir por el Fideicomiso la conveniencia de realizar la Terminación Anticipada de los Contratos Electromecánicos Auxiliares, derivado de la Terminación del Contrato de Obra Electromecánica Principal.
-•	Pendiente definir del mecanismo de financiamiento para la contratación y culminación de las obras civiles y electromecánicas.</t>
+    <t>•	07-oct: Arribaron 840 tubos de torsión acumulando un total de 1,680 piezas, asimismo llegaron 460 piezas de accionamiento de giro y componentes del sistema de seguimiento (Trackers) a la plataforma provisional en sitio.
+•	09-oct: Se emitió el cumplimiento del Hito No. 7 "Terminación de la Obra Civil de plataformas Centro de Interconexión y SE Maniobras Puerto Peñasco". Asimismo, se envió solicitud de pago al Fideicomiso, por lo que el pago estaría programado para el 25-nov-26.
+•	Del 05 al 10 de oct:  Arribaron 132 contenedores con 81,200 módulos fotovoltaicos, se tienen en sitio 114,800 piezas de 562,890 totales en la plataforma provisional en Sitio (20.39%). 
+•	Obra electromecánica: Continúan actividades de hincado de perfiles en CT-01 al CT-08 y CT-11 y CT-13 en Zona Sur del polígono de la CFV con un avance acumulado de 15,557 de 84,182 Hincas colocadas  (18.48%).
+•	Obra civil: El 05-oct-26 y el 08-oct-26 se realizaron los trabajos de colado de plantillas para cimentación, correspondientes a los CT-01 y CT-03, y CT-02 y CT-04, respectivamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte y Sur (De la subzona 1 a la 6).
+•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Norte (subzona 5, 4, 3, 2 y 1) del polígono de la CFV, con un avance de 256.80 Ha de 465.68 Ha (55.14%). Continúan trabajos de nivelación de terreno (subzona 4 y 3) con un avance de 89.34 Ha de 465.68 Ha (19.18%). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para octubre y noviembre de 2026. El hito de pago No. 12 "Pruebas y Puesta en Servicio U2" está programado para el 19 de octubre del 2026.
+•	14-oct: Se concilio y se envió para pago al Fideicomiso los avances parciales de los hitos (H5, H7 y H8) correspondientes a los suministros y montaje de las unidades, por un monto de $1.17 MDD
+•	Se requiere reforzar los frentes de obra electromecánica y puesta en servicio, así como mantener la continuidad de los trabajos en turno nocturno para mitigar riesgos al programa de ejecución. </t>
+  </si>
+  <si>
+    <t>•	25-sep: Siemens Energy entregó la ampliación de la vigencia de las garantías de anticipo y cumplimiento del Contrato Principal de la Obra Electromecánica Principal hasta el 31-oct-26.
+•	07-oct: El Fideicomiso realizó el pago del Hito No. 3 del Contrato FIEL/10670-030/2024 (COSEGO) equivalente al 7.5% del monto del Contrato ($283,236.13).
+•	09-oct: El Contratista Civil CRIBAS realizó la tercera entrega de los componentes de las compuertas del desfogue en los almacenes de la Central Termoeléctrica José Aceves Pozos.
+•	Se realizan reuniones de trabajo con Siemens Energy para cumplir con lo indicado en el Contrato de Obra Electromecánica Principal previo a la Terminación Anticipada.
+•	Pendiente la entrega-recepción de las obras civiles y el cierre del Convenio entre la CFE y el Estado de Sinaloa, así como definir el mecanismo de financiamiento para la contratación de las obras civiles y electromecánicas pendientes.</t>
   </si>
   <si>
     <t xml:space="preserve">•	Continúa pendiente la contratación de las obras civiles para la conclusión del proyecto.
-•	Se está gestionando la entrega recepción de las obras civiles, así como del finiquito los contratos a cargo de la SOP.
-•	En proceso de gestión, la formalización del Primer Convenio Modificatorio del Contrato No. F/10670-021/2024 de la obra electromecánica con Andritz.
-•	Se continua con el desarrollo y revisión de la Ingeniería correspondiente al Contrato Electromecánico. </t>
+•	Se continua con el desarrollo y revisión de la Ingeniería correspondiente al Contrato Electromecánico.
+•	08-oct: La CFE realizó actividades de conservación, inspección física y colocación de protección a los equipos electromecánicos resguardados en el almacén de Generación Hidroeléctrica Culiacán, Sinaloa.
+•	13-oct: La CFE realizó actividades de conservación, inspección física y colocación de protección a los equipos electromecánicos resguardados en el almacén de la CT José Aceves Pozos, en Mazatlán, Sinaloa. </t>
   </si>
   <si>
     <t xml:space="preserve">•	Se continua con la elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
-•	05-oct: Inicia el ensamble de las 4 secciones que conforman el Cono Fijo U1 en la plataforma 183 (zona de obras).
-•	06-oct:  Se realizó la colocación de concreto correspondiente a los segundos colados de la losa de la U3 del Desfogue (208 m³) y a la segunda alzada de la Pila 4 de la Obra de Toma (180 m³). </t>
+•	09-oct: Colado de la segunda sección de la Zapata Izquierda  del muro del Canal de Desfogue (vol. 1,100 m3)
+•	10-oct: Inician la 2a Etapa de la Construcción de la Losa de Desplante del Muro de Cierre MI.
+•	12-oct: Traslado de las Tapas del Distribuidor de la U1 del almacén 230 MD a Playa de Montaje. 
+•	13-oct: Reunión entre la CFE y el Contratista “Aristos” para establecer la fecha de presentación de la propuesta para la construcción Red de Transmisión Asociada (RTA) del P.H. Chicoasén II. Asimismo, se propuso como fecha estimada para la formalización del Contrato (20-oct-2026). </t>
   </si>
 </sst>
 </file>
@@ -1670,16 +1672,16 @@
         <v>70</v>
       </c>
       <c r="F2" s="7">
-        <v>32.54</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="G2" s="7">
-        <v>29.59</v>
+        <v>30.28</v>
       </c>
       <c r="H2" s="7">
-        <v>6.27</v>
+        <v>6.32</v>
       </c>
       <c r="I2" s="7">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="J2" s="7">
         <v>17.079999999999998</v>
@@ -1688,10 +1690,10 @@
         <v>16.89</v>
       </c>
       <c r="L2" s="7">
-        <v>9.19</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="M2" s="7">
-        <v>6.58</v>
+        <v>7.06</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
@@ -1851,28 +1853,28 @@
         <v>94</v>
       </c>
       <c r="F3" s="1">
-        <v>5.9</v>
+        <v>6.65</v>
       </c>
       <c r="G3" s="1">
-        <v>7.68</v>
+        <v>7.94</v>
       </c>
       <c r="H3" s="1">
         <v>2.83</v>
       </c>
       <c r="I3" s="1">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="J3" s="1">
-        <v>2.46</v>
+        <v>3.13</v>
       </c>
       <c r="K3" s="1">
-        <v>4.0599999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="L3" s="1">
-        <v>0.61</v>
+        <v>0.69</v>
       </c>
       <c r="M3" s="1">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -2032,10 +2034,10 @@
         <v>112</v>
       </c>
       <c r="F4" s="1">
-        <v>79.209999999999994</v>
+        <v>79.930000000000007</v>
       </c>
       <c r="G4" s="1">
-        <v>83.22</v>
+        <v>83.6</v>
       </c>
       <c r="H4" s="1">
         <v>100</v>
@@ -2047,19 +2049,19 @@
         <v>100</v>
       </c>
       <c r="K4" s="1">
-        <v>99.93</v>
+        <v>99.98</v>
       </c>
       <c r="L4" s="1">
-        <v>82.71</v>
+        <v>82.86</v>
       </c>
       <c r="M4" s="1">
-        <v>92.36</v>
+        <v>92.39</v>
       </c>
       <c r="N4" s="1">
-        <v>14.89</v>
+        <v>16.84</v>
       </c>
       <c r="O4" s="1">
-        <v>9.58</v>
+        <v>11.44</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -2173,7 +2175,7 @@
         <v>121</v>
       </c>
       <c r="F5" s="1">
-        <v>93.31</v>
+        <v>93.3</v>
       </c>
       <c r="G5" s="1">
         <v>70.02</v>
@@ -2458,25 +2460,25 @@
         <v>51.68</v>
       </c>
       <c r="G7" s="2">
-        <v>49.3</v>
+        <v>50.78</v>
       </c>
       <c r="H7" s="2">
         <v>79.56</v>
       </c>
       <c r="I7" s="2">
-        <v>59.09</v>
+        <v>59.42</v>
       </c>
       <c r="J7" s="2">
         <v>56.6</v>
       </c>
       <c r="K7" s="2">
-        <v>54.41</v>
+        <v>57.05</v>
       </c>
       <c r="L7" s="2">
         <v>47.71</v>
       </c>
       <c r="M7" s="2">
-        <v>46.35</v>
+        <v>47.4</v>
       </c>
       <c r="N7" s="2">
         <v>18.07</v>

--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5836CCC-3146-4BD1-A74A-122DB31797DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE1A049-DBB5-46A4-928D-6D1396492FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BO$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AY$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="174">
   <si>
     <t>id</t>
   </si>
@@ -83,54 +83,6 @@
     <t>realPps</t>
   </si>
   <si>
-    <t>hito1_num</t>
-  </si>
-  <si>
-    <t>hito1_titulo</t>
-  </si>
-  <si>
-    <t>hito1_fecha</t>
-  </si>
-  <si>
-    <t>hito1_desc</t>
-  </si>
-  <si>
-    <t>hito2_num</t>
-  </si>
-  <si>
-    <t>hito2_titulo</t>
-  </si>
-  <si>
-    <t>hito2_fecha</t>
-  </si>
-  <si>
-    <t>hito2_desc</t>
-  </si>
-  <si>
-    <t>hito3_num</t>
-  </si>
-  <si>
-    <t>hito3_titulo</t>
-  </si>
-  <si>
-    <t>hito3_fecha</t>
-  </si>
-  <si>
-    <t>hito3_desc</t>
-  </si>
-  <si>
-    <t>hito4_num</t>
-  </si>
-  <si>
-    <t>hito4_titulo</t>
-  </si>
-  <si>
-    <t>hito4_fecha</t>
-  </si>
-  <si>
-    <t>hito4_desc</t>
-  </si>
-  <si>
     <t>desarrollador</t>
   </si>
   <si>
@@ -405,9 +357,6 @@
   </si>
   <si>
     <t>REMCO / A de C / CRIBAS / JASE / SIEMENS/ ROAGO/ PID /AHYG /SIGTRONIC/ COSEGO/ SUMRY /COREY</t>
-  </si>
-  <si>
-    <t>$27.95 MDD</t>
   </si>
   <si>
     <t>F/10670-018/2023
@@ -451,14 +400,6 @@
     <t>$26.73 MDD</t>
   </si>
   <si>
-    <t>FIEL-10670-021/2024 ​
-// FIEL-10670-033/2024 ​
-// OPPU-EST-LP-PEST-IMSP-2003-2024 ​
-// OPPU-EST-LP-PEST-MARN-2612-2023 ​
-// OPPU-EST-LP-PEST-MARN-1912A-2023​
-// OPPU-EST-LP-PEST-MARN-2912-2023​</t>
-  </si>
-  <si>
     <t>05/01/2024</t>
   </si>
   <si>
@@ -468,9 +409,6 @@
     <t>29/12/2025</t>
   </si>
   <si>
-    <t>15/03/2029</t>
-  </si>
-  <si>
     <t>PH CHICOASÉN II</t>
   </si>
   <si>
@@ -484,9 +422,6 @@
   </si>
   <si>
     <t>Consorcio Aristos/ GE Hydro China / GE Grid</t>
-  </si>
-  <si>
-    <t>$494.83 MDD</t>
   </si>
   <si>
     <t>F/1320-004-2022​
@@ -607,97 +542,53 @@
     <t>30/12/2028</t>
   </si>
   <si>
-    <t>Limpieza y nivelación del 50% de área del polígono del Parque Fotovoltaico</t>
-  </si>
-  <si>
-    <t>20/05/26</t>
-  </si>
-  <si>
-    <t>08/08/26</t>
-  </si>
-  <si>
-    <t>$14,700,350.00</t>
-  </si>
-  <si>
-    <t>Entrega de Ingeniería Civil de detalle rev0 aprobada sin comentarios por la CFE</t>
-  </si>
-  <si>
-    <t>Limpieza y Nivelación al 100 % de área del polígono del Parque Fotovoltaico.</t>
-  </si>
-  <si>
-    <t>$**,***,***</t>
-  </si>
-  <si>
-    <t>19/07/26</t>
-  </si>
-  <si>
-    <t>Llegada a Sitio del 100% del Sistema de seguimiento (hincas y Trackers) y Equipos de acondicionamiento de potencia (Inversores)</t>
-  </si>
-  <si>
-    <t>$17,200,000.00</t>
-  </si>
-  <si>
-    <t>14/05/26</t>
-  </si>
-  <si>
-    <t>Entrega de Ingeniería Conceptual aprobada sin comentarios por la CFE</t>
-  </si>
-  <si>
-    <t>$34,400,000.00</t>
-  </si>
-  <si>
-    <t>24/05/26</t>
-  </si>
-  <si>
-    <t>Conclusión de movilización a Sitio Terminada (vallado perimetral de las oficinas temporales del área de almacén).</t>
-  </si>
-  <si>
-    <t>23/07/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega de Ingeniería Civil de detalle rev0 aprobada sin comentarios por la CFE </t>
-  </si>
-  <si>
-    <t>21/09/26</t>
-  </si>
-  <si>
-    <t>Colocación de Órdenes de Compra de equipos electromecánicos del Parque Fotovoltaico</t>
-  </si>
-  <si>
-    <t>•	07-oct: Arribaron 840 tubos de torsión acumulando un total de 1,680 piezas, asimismo llegaron 460 piezas de accionamiento de giro y componentes del sistema de seguimiento (Trackers) a la plataforma provisional en sitio.
-•	09-oct: Se emitió el cumplimiento del Hito No. 7 "Terminación de la Obra Civil de plataformas Centro de Interconexión y SE Maniobras Puerto Peñasco". Asimismo, se envió solicitud de pago al Fideicomiso, por lo que el pago estaría programado para el 25-nov-26.
-•	Del 05 al 10 de oct:  Arribaron 132 contenedores con 81,200 módulos fotovoltaicos, se tienen en sitio 114,800 piezas de 562,890 totales en la plataforma provisional en Sitio (20.39%). 
-•	Obra electromecánica: Continúan actividades de hincado de perfiles en CT-01 al CT-08 y CT-11 y CT-13 en Zona Sur del polígono de la CFV con un avance acumulado de 15,557 de 84,182 Hincas colocadas  (18.48%).
-•	Obra civil: El 05-oct-26 y el 08-oct-26 se realizaron los trabajos de colado de plantillas para cimentación, correspondientes a los CT-01 y CT-03, y CT-02 y CT-04, respectivamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte y Sur (De la subzona 1 a la 6).
-•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Norte (subzona 5, 4, 3, 2 y 1) del polígono de la CFV, con un avance de 256.80 Ha de 465.68 Ha (55.14%). Continúan trabajos de nivelación de terreno (subzona 4 y 3) con un avance de 89.34 Ha de 465.68 Ha (19.18%). </t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para octubre y noviembre de 2026. El hito de pago No. 12 "Pruebas y Puesta en Servicio U2" está programado para el 19 de octubre del 2026.
-•	14-oct: Se concilio y se envió para pago al Fideicomiso los avances parciales de los hitos (H5, H7 y H8) correspondientes a los suministros y montaje de las unidades, por un monto de $1.17 MDD
-•	Se requiere reforzar los frentes de obra electromecánica y puesta en servicio, así como mantener la continuidad de los trabajos en turno nocturno para mitigar riesgos al programa de ejecución. </t>
-  </si>
-  <si>
-    <t>•	25-sep: Siemens Energy entregó la ampliación de la vigencia de las garantías de anticipo y cumplimiento del Contrato Principal de la Obra Electromecánica Principal hasta el 31-oct-26.
-•	07-oct: El Fideicomiso realizó el pago del Hito No. 3 del Contrato FIEL/10670-030/2024 (COSEGO) equivalente al 7.5% del monto del Contrato ($283,236.13).
-•	09-oct: El Contratista Civil CRIBAS realizó la tercera entrega de los componentes de las compuertas del desfogue en los almacenes de la Central Termoeléctrica José Aceves Pozos.
-•	Se realizan reuniones de trabajo con Siemens Energy para cumplir con lo indicado en el Contrato de Obra Electromecánica Principal previo a la Terminación Anticipada.
-•	Pendiente la entrega-recepción de las obras civiles y el cierre del Convenio entre la CFE y el Estado de Sinaloa, así como definir el mecanismo de financiamiento para la contratación de las obras civiles y electromecánicas pendientes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Continúa pendiente la contratación de las obras civiles para la conclusión del proyecto.
-•	Se continua con el desarrollo y revisión de la Ingeniería correspondiente al Contrato Electromecánico.
-•	08-oct: La CFE realizó actividades de conservación, inspección física y colocación de protección a los equipos electromecánicos resguardados en el almacén de Generación Hidroeléctrica Culiacán, Sinaloa.
-•	13-oct: La CFE realizó actividades de conservación, inspección física y colocación de protección a los equipos electromecánicos resguardados en el almacén de la CT José Aceves Pozos, en Mazatlán, Sinaloa. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">•	Se continua con la elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
-•	09-oct: Colado de la segunda sección de la Zapata Izquierda  del muro del Canal de Desfogue (vol. 1,100 m3)
-•	10-oct: Inician la 2a Etapa de la Construcción de la Losa de Desplante del Muro de Cierre MI.
-•	12-oct: Traslado de las Tapas del Distribuidor de la U1 del almacén 230 MD a Playa de Montaje. 
-•	13-oct: Reunión entre la CFE y el Contratista “Aristos” para establecer la fecha de presentación de la propuesta para la construcción Red de Transmisión Asociada (RTA) del P.H. Chicoasén II. Asimismo, se propuso como fecha estimada para la formalización del Contrato (20-oct-2026). </t>
+    <t>•	Del 08 al 17-oct: Arribaron 4,410 tubos de torsión acumulando un total de 7,770 piezas, asimismo llegaron 260 piezas de accionamiento de giro acumulando un total de 1,160 piezas y componentes del sistema de seguimiento (Trackers) a la plataforma provisional en sitio.
+•	El 12 y 13-oct: Arribaron 18,900 módulos fotovoltaicos, se tienen en sitio 133,700 piezas de 562,890 totales en la plataforma provisional en Sitio (23.75%).
+•	20-oct: El Contratista emitió intenciones de Orden de Compra de los equipos : Zig-zag y sensores y equipos de medición. Así mismo, remitió invitación a las pruebas FAT del Robot de Limpieza en China. En revisión por CFE.
+•	Obra electromecánica: Continúan actividades de hincado de perfiles en Zona Sur del polígono de la CFV. Inician actividades de hincado de perfiles en Zona norte del polígono. Actualmente se tiene un avance acumulado de 23,230 de 84,182 Hincas colocadas (27.58%).
+•	Obra civil: Continúa replanteo y conformación de caminos internos y perimetrales de CFV de la sección sur. El 15-oct-26 se realizaron los trabajos de colado de plantillas para cimentación, correspondientes a los CT-06 y CT-08, así como el colado de losa de Cimentación de CT-01. Continúan trabajos de habilitado y colocación de acero y cimbra de los CT´s.</t>
+  </si>
+  <si>
+    <t>•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte y Sur (De la subzona 1 a la 7). 
+•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Sur y Norte (subzona 6 a la 1) del polígono de la CFV, con un avance de 259.45 Ha de 465.68 Ha (55.71%). Continúan trabajos de nivelación de terreno (subzona 4  a la 1) con un avance de 102.54 Ha de 465.68 Ha (22.02%).  Continúan actividades de conformación de plataforma de Centro de Interconexión de Sec. IV con un avance de 2/9 capas (16.89%).</t>
+  </si>
+  <si>
+    <t>•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para oct y nov-26. El hito de pago No. 12 "Pruebas y Puesta en Servicio U2" está programado para el 18-oct-26.
+•	16-oct-26: HITO 12 – INCUMPLIMIENTO: Mediante escrito del 16 de octubre de 2026, el Contratista notificó el incumplimiento del Hito de Pago No. 12  del 18-oct-26, atribuyéndolo a pendientes de la Contratante (línea de transmisión y base de datos de CENACE). 
+•	18-oct-26: HITO 12 Mediante escrito del 18 de octubre de 2026, la Residencia de Obra respondió que el incumplimiento es responsabilidad del Contratista, anexando la relación de pendientes a su cargo para la ejecución de las Pruebas.
+•	Como medida de mitigación del atraso en las Pruebas y Puesta en Marcha, se solicitó al Contratista incrementar el personal en los frentes de obra electromecánica, así como, la implementación del turno nocturno, y reforzar la coordinación Contratante-Contratista con CENACE y CFE Transmisión.</t>
+  </si>
+  <si>
+    <t>•	14-oct: En reunión técnica se concilió el Valor de Terminación (VT) del Contrato FIEL/10670-018/2023, con Siemens Energy, que asciende a USD 2,762,301.75 equivalente a 16.25% del monto del Contrato.
+•	Mediante escrito del 16-oct-26, la CFE dio respuesta al comunicado de fecha 04-ago-26 de Siemens Energy, indicando que las observaciones a la soldadura de los Reductores Rectos de las turbinas 1 y 2 no afectan el funcionamiento hidráulico.
+•	Mediante escrito del 20-oct-26, la CFE notificó a la PROFEPA que concluyeron los trabajos de Cambio de Uso de Suelo en Terrenos Forestales para el PEH Picachos.
+•	20-oct: Reunión entre la SOP-CFE dando seguimiento a los compromisos del proceso de Entrega Recepción de las Obras Civiles, la SOP informó que no hay avances en el finiquito de los contratos civiles del Proyecto.
+•	Pendiente el cierre del Convenio entre la CFE y el Estado de Sinaloa, así como definir el mecanismo de financiamiento para la contratación de las obras civiles y electromecánicas pendientes.</t>
+  </si>
+  <si>
+    <t>$27.09 MDD</t>
+  </si>
+  <si>
+    <t>31/03/2029</t>
+  </si>
+  <si>
+    <t>FIEL-10670-021/2024 ​</t>
+  </si>
+  <si>
+    <t>•	Continúa pendiente la contratación de las obras civiles para la conclusión del proyecto.
+•	La CFE da seguimiento a los cierres administrativos de los contratos de Obra Civil Adjudicados al Gobierno del estado de Sinaloa.  
+•	La CFE realizó actividades de conservación, inspección física y colocación de protección a los equipos electromecánicos resguardados en el almacén de Generación Hidroeléctrica Culiacán, Sinaloa. 
+•	La CFE oficializa el almacenamiento y resguardo de los equipos electromecánicos del PEH Amata mediante el Oficio del 15-oct-26, a la Administración de la CT José Aceves Pozos, en Mazatlán, Sinaloa.
+•	Se continua con el desarrollo y revisión de la Ingeniería de detalle correspondiente al Contrato Electromecánico.</t>
+  </si>
+  <si>
+    <t>$574.22 MDD</t>
+  </si>
+  <si>
+    <t>•	Se continua con la elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
+•	15-oct: Colado de una sección del Cimacio (parte superior o cresta)  aguas Arriba del Vertedor de Servicio (Vol. 720 m3).
+•	19-oct: Inicia el ensamble de la tubería de acero de 1.6 m de diámetro para el Gasto Ecológico en el Muro de Cierre Toma Ecológica. 
+•	19-oct: Colado de la sección B de Cimacio (parte superior o cresta) del Vertedor de Servicio (Vol. 405 m3).</t>
   </si>
 </sst>
 </file>
@@ -788,7 +679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -972,58 +863,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1036,7 +875,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1053,7 +892,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1077,12 +915,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -1390,7 +1222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BO7"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1408,52 +1240,36 @@
     <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="35" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="31" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17" bestFit="1" customWidth="1"/>
-    <col min="57" max="63" width="16" bestFit="1" customWidth="1"/>
-    <col min="64" max="67" width="16" customWidth="1"/>
+    <col min="16" max="16" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17" bestFit="1" customWidth="1"/>
+    <col min="41" max="47" width="16" bestFit="1" customWidth="1"/>
+    <col min="48" max="51" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1499,85 +1315,85 @@
         <v>14</v>
       </c>
       <c r="P1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="AC1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AE1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AF1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AG1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AH1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AI1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AK1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AL1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AM1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AN1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AO1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AP1" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AN1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AO1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP1" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="AQ1" s="5" t="s">
         <v>34</v>
@@ -1603,97 +1419,49 @@
       <c r="AX1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AY1" s="5" t="s">
+      <c r="AY1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AZ1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="BA1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="BB1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BC1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="BD1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BE1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="BF1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="BG1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="BH1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="BI1" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="BJ1" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="BK1" s="5" t="s">
+      <c r="E2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="BL1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="BM1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="BN1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="BO1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>70</v>
-      </c>
       <c r="F2" s="7">
-        <v>33.119999999999997</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="G2" s="7">
-        <v>30.28</v>
+        <v>31.37</v>
       </c>
       <c r="H2" s="7">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="I2" s="7">
-        <v>6.33</v>
+        <v>6.46</v>
       </c>
       <c r="J2" s="7">
-        <v>17.079999999999998</v>
+        <v>17.79</v>
       </c>
       <c r="K2" s="7">
-        <v>16.89</v>
+        <v>17.29</v>
       </c>
       <c r="L2" s="7">
-        <v>9.7200000000000006</v>
+        <v>10.15</v>
       </c>
       <c r="M2" s="7">
-        <v>7.06</v>
+        <v>7.62</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
@@ -1701,180 +1469,132 @@
       <c r="O2" s="7">
         <v>0</v>
       </c>
-      <c r="P2" s="7">
-        <v>6</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="R2" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="T2" s="7">
-        <v>5</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="W2" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="X2" s="7">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB2" s="7">
-        <v>8</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="AD2" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="AE2" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="AF2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG2" s="10" t="s">
+      <c r="P2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="T2" s="9">
+        <v>728</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK2" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AH2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ2" s="10">
-        <v>728</v>
-      </c>
-      <c r="AK2" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL2" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM2" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AN2" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO2" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP2" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR2" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AT2" s="11" t="s">
+      <c r="AO2" s="10"/>
+      <c r="AP2" s="10"/>
+      <c r="AQ2" s="10"/>
+      <c r="AR2" s="10"/>
+      <c r="AS2" s="10"/>
+      <c r="AT2" s="10"/>
+      <c r="AU2" s="10"/>
+      <c r="AV2" s="10"/>
+      <c r="AW2" s="10"/>
+      <c r="AX2" s="10"/>
+      <c r="AY2" s="11"/>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="AU2" s="11" t="s">
+      <c r="C3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="AV2" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AX2" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AY2" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ2" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="BA2" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="BB2" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="BC2" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="BD2" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="BE2" s="11"/>
-      <c r="BF2" s="11"/>
-      <c r="BG2" s="11"/>
-      <c r="BH2" s="11"/>
-      <c r="BI2" s="11"/>
-      <c r="BJ2" s="11"/>
-      <c r="BK2" s="11"/>
-      <c r="BL2" s="11"/>
-      <c r="BM2" s="11"/>
-      <c r="BN2" s="11"/>
-      <c r="BO2" s="12"/>
-    </row>
-    <row r="3" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>94</v>
-      </c>
       <c r="F3" s="1">
-        <v>6.65</v>
+        <v>7.75</v>
       </c>
       <c r="G3" s="1">
-        <v>7.94</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="H3" s="1">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="I3" s="1">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="J3" s="1">
-        <v>3.13</v>
+        <v>4.08</v>
       </c>
       <c r="K3" s="1">
         <v>4.0999999999999996</v>
       </c>
       <c r="L3" s="1">
-        <v>0.69</v>
+        <v>0.8</v>
       </c>
       <c r="M3" s="1">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -1882,303 +1602,239 @@
       <c r="O3" s="1">
         <v>0</v>
       </c>
-      <c r="P3" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="R3" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="S3" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="T3" s="1">
+      <c r="P3" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" s="12">
+        <v>730</v>
+      </c>
+      <c r="U3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="X3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB3" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC3" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD3" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE3" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF3" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG3" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ3" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO3" s="13"/>
+      <c r="AP3" s="13"/>
+      <c r="AQ3" s="13"/>
+      <c r="AR3" s="13"/>
+      <c r="AS3" s="13"/>
+      <c r="AT3" s="13"/>
+      <c r="AU3" s="13"/>
+      <c r="AV3" s="13"/>
+      <c r="AW3" s="13"/>
+      <c r="AX3" s="13"/>
+      <c r="AY3" s="14"/>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
         <v>3</v>
       </c>
-      <c r="U3" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="W3" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="X3" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z3" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>4</v>
-      </c>
-      <c r="AC3" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="AD3" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF3" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="AG3" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH3" s="13" t="s">
+      <c r="B4" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AI3" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ3" s="13">
-        <v>730</v>
-      </c>
-      <c r="AK3" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="AL3" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM3" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AN3" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO3" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP3" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ3" s="14" t="s">
+      <c r="E4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="AR3" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AT3" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AU3" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="AV3" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="AW3" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AX3" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="AY3" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ3" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="BA3" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="BB3" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="BC3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="BD3" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="BE3" s="14"/>
-      <c r="BF3" s="14"/>
-      <c r="BG3" s="14"/>
-      <c r="BH3" s="14"/>
-      <c r="BI3" s="14"/>
-      <c r="BJ3" s="14"/>
-      <c r="BK3" s="14"/>
-      <c r="BL3" s="14"/>
-      <c r="BM3" s="14"/>
-      <c r="BN3" s="14"/>
-      <c r="BO3" s="15"/>
-    </row>
-    <row r="4" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A4" s="26">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>112</v>
-      </c>
       <c r="F4" s="1">
-        <v>79.930000000000007</v>
+        <v>80.66</v>
       </c>
       <c r="G4" s="1">
-        <v>83.6</v>
+        <v>83.95</v>
       </c>
       <c r="H4" s="1">
         <v>100</v>
       </c>
       <c r="I4" s="1">
-        <v>99.37</v>
+        <v>99.65</v>
       </c>
       <c r="J4" s="1">
         <v>100</v>
       </c>
       <c r="K4" s="1">
-        <v>99.98</v>
+        <v>100</v>
       </c>
       <c r="L4" s="1">
-        <v>82.86</v>
+        <v>82.95</v>
       </c>
       <c r="M4" s="1">
-        <v>92.39</v>
+        <v>92.51</v>
       </c>
       <c r="N4" s="1">
-        <v>16.84</v>
+        <v>21.18</v>
       </c>
       <c r="O4" s="1">
-        <v>11.44</v>
-      </c>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="AG4" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="AH4" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI4" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ4" s="16">
+        <v>12.97</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="T4" s="15">
         <v>1420</v>
       </c>
-      <c r="AK4" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL4" s="13"/>
-      <c r="AM4" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN4" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO4" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP4" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="AQ4" s="13"/>
-      <c r="AR4" s="13"/>
-      <c r="AS4" s="13"/>
-      <c r="AT4" s="13"/>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="13"/>
-      <c r="AW4" s="13"/>
-      <c r="AX4" s="13"/>
-      <c r="AY4" s="13"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="13"/>
-      <c r="BC4" s="13"/>
-      <c r="BD4" s="13"/>
-      <c r="BE4" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="BF4" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="BG4" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="BH4" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="BI4" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="BJ4" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="BK4" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="BL4" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="BM4" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN4" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="BO4" s="15" t="s">
-        <v>171</v>
+      <c r="U4" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="V4" s="12"/>
+      <c r="W4" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="X4" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="12"/>
+      <c r="AL4" s="12"/>
+      <c r="AM4" s="12"/>
+      <c r="AN4" s="12"/>
+      <c r="AO4" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AP4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="AQ4" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR4" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS4" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="AT4" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AU4" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="AV4" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AW4" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="AX4" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY4" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>121</v>
+      <c r="B5" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="F5" s="1">
         <v>93.3</v>
       </c>
       <c r="G5" s="1">
-        <v>70.02</v>
+        <v>74.47</v>
       </c>
       <c r="H5" s="1">
         <v>100</v>
@@ -2204,128 +1860,112 @@
       <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="AG5" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH5" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI5" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ5" s="16">
+      <c r="P5" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="T5" s="15">
         <v>1720</v>
       </c>
-      <c r="AK5" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN5" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="AO5" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="AP5" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ5" s="13"/>
-      <c r="AR5" s="13"/>
-      <c r="AS5" s="13"/>
-      <c r="AT5" s="13"/>
-      <c r="AU5" s="13"/>
-      <c r="AV5" s="13"/>
-      <c r="AW5" s="13"/>
-      <c r="AX5" s="13"/>
-      <c r="AY5" s="13"/>
-      <c r="AZ5" s="13"/>
-      <c r="BA5" s="13"/>
-      <c r="BB5" s="13"/>
-      <c r="BC5" s="13"/>
-      <c r="BD5" s="13"/>
-      <c r="BE5" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="BF5" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="BG5" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="BH5" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="BI5" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="BJ5" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK5" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL5" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM5" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="BN5" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO5" s="15" t="s">
-        <v>160</v>
+      <c r="U5" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="V5" s="12"/>
+      <c r="W5" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12"/>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="12"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AM5" s="12"/>
+      <c r="AN5" s="12"/>
+      <c r="AO5" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP5" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ5" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR5" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS5" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="AT5" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU5" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV5" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW5" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX5" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="AY5" s="14" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>131</v>
+      <c r="B6" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="F6" s="1">
         <v>100</v>
       </c>
       <c r="G6" s="1">
-        <v>33.67</v>
+        <v>32.21</v>
       </c>
       <c r="H6" s="1">
         <v>100</v>
       </c>
       <c r="I6" s="1">
-        <v>68</v>
+        <v>64.92</v>
       </c>
       <c r="J6" s="1">
         <v>100</v>
@@ -2345,122 +1985,106 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="AG6" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH6" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI6" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="AJ6" s="16">
+      <c r="P6" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="S6" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="T6" s="15">
         <v>1896</v>
       </c>
-      <c r="AK6" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="AN6" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="AO6" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="AP6" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="13"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="13"/>
-      <c r="BE6" s="14">
+      <c r="U6" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="V6" s="12"/>
+      <c r="W6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="X6" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y6" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z6" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="12"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="12"/>
+      <c r="AN6" s="12"/>
+      <c r="AO6" s="13">
         <v>10</v>
       </c>
-      <c r="BF6" s="14">
+      <c r="AP6" s="13">
         <v>46.85</v>
       </c>
-      <c r="BG6" s="14">
+      <c r="AQ6" s="13">
         <v>54.5</v>
       </c>
-      <c r="BH6" s="14">
+      <c r="AR6" s="13">
         <v>2</v>
       </c>
-      <c r="BI6" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="BJ6" s="14">
+      <c r="AS6" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AT6" s="13">
         <v>11.5</v>
       </c>
-      <c r="BK6" s="14">
+      <c r="AU6" s="13">
         <v>50</v>
       </c>
-      <c r="BL6" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="BM6" s="14">
+      <c r="AV6" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="AW6" s="13">
         <v>31.48</v>
       </c>
-      <c r="BN6" s="14">
+      <c r="AX6" s="13">
         <v>21.193000000000001</v>
       </c>
-      <c r="BO6" s="15">
+      <c r="AY6" s="14">
         <v>8944</v>
       </c>
     </row>
-    <row r="7" spans="1:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27">
+    <row r="7" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>142</v>
+      <c r="B7" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="F7" s="2">
-        <v>51.68</v>
+        <v>46.19</v>
       </c>
       <c r="G7" s="2">
-        <v>50.78</v>
+        <v>44.56</v>
       </c>
       <c r="H7" s="2">
         <v>79.56</v>
@@ -2486,103 +2110,87 @@
       <c r="O7" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="AG7" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="AH7" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI7" s="17" t="s">
+      <c r="P7" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q7" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="T7" s="17">
+        <v>1750</v>
+      </c>
+      <c r="U7" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="V7" s="16"/>
+      <c r="W7" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="X7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z7" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="16"/>
+      <c r="AI7" s="16"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
+      <c r="AL7" s="16"/>
+      <c r="AM7" s="16"/>
+      <c r="AN7" s="16"/>
+      <c r="AO7" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="AP7" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="AJ7" s="18">
-        <v>1750</v>
-      </c>
-      <c r="AK7" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL7" s="17"/>
-      <c r="AM7" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="AN7" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO7" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="AP7" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AQ7" s="17"/>
-      <c r="AR7" s="17"/>
-      <c r="AS7" s="17"/>
-      <c r="AT7" s="17"/>
-      <c r="AU7" s="17"/>
-      <c r="AV7" s="17"/>
-      <c r="AW7" s="17"/>
-      <c r="AX7" s="17"/>
-      <c r="AY7" s="17"/>
-      <c r="AZ7" s="17"/>
-      <c r="BA7" s="17"/>
-      <c r="BB7" s="17"/>
-      <c r="BC7" s="17"/>
-      <c r="BD7" s="17"/>
-      <c r="BE7" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="BF7" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="BG7" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="BH7" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="BI7" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="BJ7" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="BK7" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="BL7" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="BM7" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="BN7" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="BO7" s="20" t="s">
-        <v>172</v>
+      <c r="AQ7" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR7" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="AS7" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="AT7" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="AU7" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="AV7" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="AW7" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX7" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="AY7" s="19" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BO1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AY1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -2081,7 +2081,7 @@
         <v>123</v>
       </c>
       <c r="F7" s="2">
-        <v>46.19</v>
+        <v>46.14</v>
       </c>
       <c r="G7" s="2">
         <v>44.56</v>

--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE1A049-DBB5-46A4-928D-6D1396492FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261A08FB-9AAF-4F64-B6DC-DA18C87F3602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AY$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AZ$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="176">
   <si>
     <t>id</t>
   </si>
@@ -542,53 +542,58 @@
     <t>30/12/2028</t>
   </si>
   <si>
-    <t>•	Del 08 al 17-oct: Arribaron 4,410 tubos de torsión acumulando un total de 7,770 piezas, asimismo llegaron 260 piezas de accionamiento de giro acumulando un total de 1,160 piezas y componentes del sistema de seguimiento (Trackers) a la plataforma provisional en sitio.
-•	El 12 y 13-oct: Arribaron 18,900 módulos fotovoltaicos, se tienen en sitio 133,700 piezas de 562,890 totales en la plataforma provisional en Sitio (23.75%).
-•	20-oct: El Contratista emitió intenciones de Orden de Compra de los equipos : Zig-zag y sensores y equipos de medición. Así mismo, remitió invitación a las pruebas FAT del Robot de Limpieza en China. En revisión por CFE.
-•	Obra electromecánica: Continúan actividades de hincado de perfiles en Zona Sur del polígono de la CFV. Inician actividades de hincado de perfiles en Zona norte del polígono. Actualmente se tiene un avance acumulado de 23,230 de 84,182 Hincas colocadas (27.58%).
-•	Obra civil: Continúa replanteo y conformación de caminos internos y perimetrales de CFV de la sección sur. El 15-oct-26 se realizaron los trabajos de colado de plantillas para cimentación, correspondientes a los CT-06 y CT-08, así como el colado de losa de Cimentación de CT-01. Continúan trabajos de habilitado y colocación de acero y cimbra de los CT´s.</t>
-  </si>
-  <si>
-    <t>•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna dentro del polígono de la CFV Zona Norte y Sur (De la subzona 1 a la 7). 
-•	Obra civil: Continúan los trabajos de limpieza del terreno en la Zona Sur y Norte (subzona 6 a la 1) del polígono de la CFV, con un avance de 259.45 Ha de 465.68 Ha (55.71%). Continúan trabajos de nivelación de terreno (subzona 4  a la 1) con un avance de 102.54 Ha de 465.68 Ha (22.02%).  Continúan actividades de conformación de plataforma de Centro de Interconexión de Sec. IV con un avance de 2/9 capas (16.89%).</t>
-  </si>
-  <si>
-    <t>•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2, programadas para oct y nov-26. El hito de pago No. 12 "Pruebas y Puesta en Servicio U2" está programado para el 18-oct-26.
-•	16-oct-26: HITO 12 – INCUMPLIMIENTO: Mediante escrito del 16 de octubre de 2026, el Contratista notificó el incumplimiento del Hito de Pago No. 12  del 18-oct-26, atribuyéndolo a pendientes de la Contratante (línea de transmisión y base de datos de CENACE). 
-•	18-oct-26: HITO 12 Mediante escrito del 18 de octubre de 2026, la Residencia de Obra respondió que el incumplimiento es responsabilidad del Contratista, anexando la relación de pendientes a su cargo para la ejecución de las Pruebas.
-•	Como medida de mitigación del atraso en las Pruebas y Puesta en Marcha, se solicitó al Contratista incrementar el personal en los frentes de obra electromecánica, así como, la implementación del turno nocturno, y reforzar la coordinación Contratante-Contratista con CENACE y CFE Transmisión.</t>
-  </si>
-  <si>
-    <t>•	14-oct: En reunión técnica se concilió el Valor de Terminación (VT) del Contrato FIEL/10670-018/2023, con Siemens Energy, que asciende a USD 2,762,301.75 equivalente a 16.25% del monto del Contrato.
-•	Mediante escrito del 16-oct-26, la CFE dio respuesta al comunicado de fecha 04-ago-26 de Siemens Energy, indicando que las observaciones a la soldadura de los Reductores Rectos de las turbinas 1 y 2 no afectan el funcionamiento hidráulico.
-•	Mediante escrito del 20-oct-26, la CFE notificó a la PROFEPA que concluyeron los trabajos de Cambio de Uso de Suelo en Terrenos Forestales para el PEH Picachos.
-•	20-oct: Reunión entre la SOP-CFE dando seguimiento a los compromisos del proceso de Entrega Recepción de las Obras Civiles, la SOP informó que no hay avances en el finiquito de los contratos civiles del Proyecto.
+    <t>$27.09 MDD</t>
+  </si>
+  <si>
+    <t>31/03/2029</t>
+  </si>
+  <si>
+    <t>FIEL-10670-021/2024 ​</t>
+  </si>
+  <si>
+    <t>$574.22 MDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	23 a 26-oct 2026: Arribaron al Sitio un total de 24,733 hincas, acumulando un total de 85,000 hincas en Sitio de 84,182 (100%), el excedente se considera como refacciones por algún daño durante el proceso de hincado. Asimismo, se tiene un promedio de suministro de componentes de los Trackers del 17.99% en la plataforma provisional en sitio.
+•	27-oct-26: Iniciaron las pruebas FAT del Transformador de Potencia en las instalaciones del proveedor en Shenyang, China.
+•	Obra electromecánica: Continúan el hincado de perfiles en zona Sur y zona Norte del polígono, con un avance acumulado de 31,358 de 84,182 Hincas colocadas (37.41%). 
+•	Obra civil: Continúa conformación de caminos provisionales en la sección sur del polígono. Asimismo, se realizaron los colados de cimentación y de plantilla de cimentación de los Centros de Transformación CT-04, CT-10, CT-11 y CT-08. Continúan trabajos de habilitado y colocación de acero y cimbra para los CT´s. </t>
+  </si>
+  <si>
+    <t>•	Ambiental: Continúan los trabajos de rescate y reubicación de flora y fauna en Zona Norte y Sur del polígono (De la subzona 1 a la 7). 
+•	Obra civil: continúa la delimitación de sub-zonas del polígono, continúan actividades de desmonte y limpieza del polígono con un avance de 266.12 Ha de 465.7 Ha (57.15%), asimismo continúa la nivelación del terreno con un avance de 93.30 Ha de 465.7 Ha (24.58%).</t>
+  </si>
+  <si>
+    <t>•	Continúan las actividades de montaje de equipos y sistemas electromecánicos para la puesta en marcha y entrada en operación de las unidades U1 y U2. El Hito de pago No. 12 "Pruebas y Puesta en Servicio U2" tiene fecha estimada para el 18-oct-26.
+•	Como consecuencia del incumplimiento del Hito No. 12, previsto para el 18 de octubre de 2026, se están realizando mesas de trabajo para la revisión del programa detallado de las Pruebas de Puesta en Servicio. El Contratista y su subcontratista continúan con el análisis y definición de las actividades correspondientes, con el compromiso de presentar una propuesta actualizada a la Contratante en el corto plazo.
+•	Como medida de mitigación del atraso en las Pruebas y Puesta en Marcha, la CFE solicitó en reuniones de trabajo al Contratista incrementar el personal en los frentes de obra electromecánica, así como, la implementación del turno nocturno, y reforzar la coordinación Contratante-Contratista con CENACE y CFE Transmisión.</t>
+  </si>
+  <si>
+    <t>•	El 21-oct-26, la CFE registró el trámite del permiso de construcción del Proyecto en la plataforma digital Buzón del Agua de CONAGUA; así mismo, el 27-oct-26 mediante escrito se notificó al Organismo de Cuenca Pacifico Norte el inicio del trámite. 
+•	El 21-oct-26, el Fideicomiso solicitó mediante escrito a Siemens Energy la ampliación de las garantías de cumplimiento y anticipo con vigencia a la conclusión del Contrato.
+•	El 27-oct-26, vía correo electrónico el Contratista COSEGO remitió el complemento de pago del Hito No. 3 amparado con la factura F-1146 del Contrato FIEL/10670-030/2024 por un monto de USD $244,169.08.
+•	La CFE analiza realizar la  recisión del Contrato FIEL/10670-032/2024 (Equipamiento Taller Mecánico) derivado de los Incumplimientos del Contratista COREY.
 •	Pendiente el cierre del Convenio entre la CFE y el Estado de Sinaloa, así como definir el mecanismo de financiamiento para la contratación de las obras civiles y electromecánicas pendientes.</t>
   </si>
   <si>
-    <t>$27.09 MDD</t>
-  </si>
-  <si>
-    <t>31/03/2029</t>
-  </si>
-  <si>
-    <t>FIEL-10670-021/2024 ​</t>
-  </si>
-  <si>
-    <t>•	Continúa pendiente la contratación de las obras civiles para la conclusión del proyecto.
-•	La CFE da seguimiento a los cierres administrativos de los contratos de Obra Civil Adjudicados al Gobierno del estado de Sinaloa.  
+    <t>•	Continúa pendiente la contratación de las obras civiles para la conclusión del proyecto.  
 •	La CFE realizó actividades de conservación, inspección física y colocación de protección a los equipos electromecánicos resguardados en el almacén de Generación Hidroeléctrica Culiacán, Sinaloa. 
-•	La CFE oficializa el almacenamiento y resguardo de los equipos electromecánicos del PEH Amata mediante el Oficio del 15-oct-26, a la Administración de la CT José Aceves Pozos, en Mazatlán, Sinaloa.
+•	Mediante escrito de fecha 26-oct-26 el Contratista Andritz envió el listado de materiales y equipos que suministrará correspondientes al generador Unidad 1 y 2, provenientes de Reinosa, España. El arribo de los componentes tiene fecha estimada a finales de noviembre 2026.
+•	La CFE continúa realizando actividades de conservación, inspección física y colocación de protección a los equipos electromecánicos resguardados en el almacén de Generación Hidroeléctrica Culiacán, Sinaloa.
 •	Se continua con el desarrollo y revisión de la Ingeniería de detalle correspondiente al Contrato Electromecánico.</t>
   </si>
   <si>
-    <t>$574.22 MDD</t>
-  </si>
-  <si>
     <t>•	Se continua con la elaboración e integración del Análisis de Viabilidad del P.H. Chicoasén II, para la solicitud de recursos para finalizar la obra.
-•	15-oct: Colado de una sección del Cimacio (parte superior o cresta)  aguas Arriba del Vertedor de Servicio (Vol. 720 m3).
-•	19-oct: Inicia el ensamble de la tubería de acero de 1.6 m de diámetro para el Gasto Ecológico en el Muro de Cierre Toma Ecológica. 
-•	19-oct: Colado de la sección B de Cimacio (parte superior o cresta) del Vertedor de Servicio (Vol. 405 m3).</t>
+•	22-oct: Colado de la Etapa 3 de la Elev. 177.67 a 180.03 del Empaque del Cono de Aspiración (ECA) U1 (Vol. 1300 m3).
+•	23-oct: Montaje de la Columna Fija Lateral Derecha U2 a la Columna Fija Inferior en su posición final en zona de unidades. 
+•	26-oct: Colado de la Etapa 3 de la Elev. 180.03 a 183.13  del ECA U1 (Vol. 812 m3).
+•	27-oct: Traslado de la Nariz de Bulbo U2 de almacén 205 MI a Plataforma 183 (zona de Obras).</t>
+  </si>
+  <si>
+    <t>video</t>
+  </si>
+  <si>
+    <t>data/VIDEOS/CHICOASEN.mp4</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1230,45 +1235,46 @@
     <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="17" bestFit="1" customWidth="1"/>
-    <col min="41" max="47" width="16" bestFit="1" customWidth="1"/>
-    <col min="48" max="51" width="16" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17" bestFit="1" customWidth="1"/>
+    <col min="42" max="48" width="16" bestFit="1" customWidth="1"/>
+    <col min="49" max="52" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1284,146 +1290,149 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AN1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AO1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AR1" s="5" t="s">
+      <c r="AS1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AS1" s="5" t="s">
+      <c r="AT1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AT1" s="5" t="s">
+      <c r="AU1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="5" t="s">
+      <c r="AV1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="5" t="s">
+      <c r="AW1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AW1" s="5" t="s">
+      <c r="AX1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AX1" s="5" t="s">
+      <c r="AY1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -1439,112 +1448,112 @@
       <c r="E2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="7">
-        <v>34.299999999999997</v>
-      </c>
+      <c r="F2" s="20"/>
       <c r="G2" s="7">
-        <v>31.37</v>
+        <v>36.08</v>
       </c>
       <c r="H2" s="7">
+        <v>32.17</v>
+      </c>
+      <c r="I2" s="7">
         <v>6.36</v>
       </c>
-      <c r="I2" s="7">
+      <c r="J2" s="7">
         <v>6.46</v>
       </c>
-      <c r="J2" s="7">
-        <v>17.79</v>
-      </c>
       <c r="K2" s="7">
-        <v>17.29</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="L2" s="7">
-        <v>10.15</v>
+        <v>17.86</v>
       </c>
       <c r="M2" s="7">
-        <v>7.62</v>
+        <v>10.28</v>
       </c>
       <c r="N2" s="7">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="O2" s="7">
         <v>0</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q2" s="9" t="s">
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="S2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="T2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="T2" s="9">
+      <c r="U2" s="9">
         <v>728</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="W2" s="10" t="s">
         <v>73</v>
       </c>
       <c r="X2" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Z2" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="AA2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AB2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AC2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AD2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AE2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AF2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AG2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AG2" s="9" t="s">
+      <c r="AH2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AH2" s="10" t="s">
+      <c r="AI2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AJ2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AK2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AL2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="AL2" s="9" t="s">
+      <c r="AM2" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AM2" s="9" t="s">
+      <c r="AN2" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AN2" s="9" t="s">
+      <c r="AO2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AO2" s="10"/>
       <c r="AP2" s="10"/>
       <c r="AQ2" s="10"/>
       <c r="AR2" s="10"/>
@@ -1554,9 +1563,10 @@
       <c r="AV2" s="10"/>
       <c r="AW2" s="10"/>
       <c r="AX2" s="10"/>
-      <c r="AY2" s="11"/>
+      <c r="AY2" s="10"/>
+      <c r="AZ2" s="11"/>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" s="25">
         <v>2</v>
       </c>
@@ -1572,112 +1582,112 @@
       <c r="E3" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="1">
-        <v>7.75</v>
-      </c>
+      <c r="F3" s="21"/>
       <c r="G3" s="1">
-        <v>8.2200000000000006</v>
+        <v>9.75</v>
       </c>
       <c r="H3" s="1">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="I3" s="1">
         <v>2.87</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>3.21</v>
       </c>
-      <c r="J3" s="1">
-        <v>4.08</v>
-      </c>
       <c r="K3" s="1">
-        <v>4.0999999999999996</v>
+        <v>5.97</v>
       </c>
       <c r="L3" s="1">
-        <v>0.8</v>
+        <v>5.37</v>
       </c>
       <c r="M3" s="1">
         <v>0.91</v>
       </c>
       <c r="N3" s="1">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O3" s="1">
         <v>0</v>
       </c>
-      <c r="P3" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q3" s="12" t="s">
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="R3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="S3" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="T3" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="12">
+      <c r="U3" s="12">
         <v>730</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="V3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="W3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="W3" s="13" t="s">
+      <c r="X3" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="X3" s="13" t="s">
+      <c r="Y3" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="Y3" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="Z3" s="13" t="s">
         <v>92</v>
       </c>
       <c r="AA3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AB3" s="13" t="s">
+      <c r="AC3" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AD3" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AD3" s="13" t="s">
+      <c r="AE3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AF3" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AF3" s="13" t="s">
+      <c r="AG3" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AG3" s="12" t="s">
+      <c r="AH3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="AH3" s="13" t="s">
+      <c r="AI3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AI3" s="13" t="s">
+      <c r="AJ3" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AJ3" s="13" t="s">
+      <c r="AK3" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AK3" s="13" t="s">
+      <c r="AL3" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="AL3" s="12" t="s">
+      <c r="AM3" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AM3" s="12" t="s">
+      <c r="AN3" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AN3" s="12" t="s">
+      <c r="AO3" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AO3" s="13"/>
       <c r="AP3" s="13"/>
       <c r="AQ3" s="13"/>
       <c r="AR3" s="13"/>
@@ -1687,9 +1697,10 @@
       <c r="AV3" s="13"/>
       <c r="AW3" s="13"/>
       <c r="AX3" s="13"/>
-      <c r="AY3" s="14"/>
+      <c r="AY3" s="13"/>
+      <c r="AZ3" s="14"/>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>3</v>
       </c>
@@ -1705,68 +1716,68 @@
       <c r="E4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="1">
-        <v>80.66</v>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="1">
-        <v>83.95</v>
+        <v>81.39</v>
       </c>
       <c r="H4" s="1">
+        <v>84.36</v>
+      </c>
+      <c r="I4" s="1">
         <v>100</v>
       </c>
-      <c r="I4" s="1">
-        <v>99.65</v>
-      </c>
       <c r="J4" s="1">
-        <v>100</v>
+        <v>99.63</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
       </c>
       <c r="L4" s="1">
-        <v>82.95</v>
+        <v>100</v>
       </c>
       <c r="M4" s="1">
-        <v>92.51</v>
+        <v>83.08</v>
       </c>
       <c r="N4" s="1">
-        <v>21.18</v>
+        <v>92.58</v>
       </c>
       <c r="O4" s="1">
-        <v>12.97</v>
-      </c>
-      <c r="P4" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q4" s="12" t="s">
+        <v>25.84</v>
+      </c>
+      <c r="P4" s="1">
+        <v>15.41</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="R4" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="T4" s="15">
+      <c r="U4" s="15">
         <v>1420</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="V4" s="12"/>
-      <c r="W4" s="13" t="s">
+      <c r="W4" s="12"/>
+      <c r="X4" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="Y4" s="13" t="s">
         <v>101</v>
-      </c>
-      <c r="Y4" s="13" t="s">
-        <v>102</v>
       </c>
       <c r="Z4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AA4" s="12"/>
+      <c r="AA4" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1780,41 +1791,42 @@
       <c r="AL4" s="12"/>
       <c r="AM4" s="12"/>
       <c r="AN4" s="12"/>
-      <c r="AO4" s="13" t="s">
+      <c r="AO4" s="12"/>
+      <c r="AP4" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AP4" s="13" t="s">
+      <c r="AQ4" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AQ4" s="13" t="s">
+      <c r="AR4" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="AR4" s="13" t="s">
+      <c r="AS4" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AS4" s="13" t="s">
+      <c r="AT4" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="AT4" s="13" t="s">
+      <c r="AU4" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="AU4" s="13" t="s">
+      <c r="AV4" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="AV4" s="13" t="s">
+      <c r="AW4" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AW4" s="13" t="s">
+      <c r="AX4" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AX4" s="13" t="s">
+      <c r="AY4" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="AY4" s="14" t="s">
+      <c r="AZ4" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -1830,14 +1842,12 @@
       <c r="E5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="21"/>
+      <c r="G5" s="1">
         <v>93.3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>74.47</v>
-      </c>
-      <c r="H5" s="1">
-        <v>100</v>
       </c>
       <c r="I5" s="1">
         <v>100</v>
@@ -1846,52 +1856,54 @@
         <v>100</v>
       </c>
       <c r="K5" s="1">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
         <v>93.19</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>93.37</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>63.5</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q5" s="12" t="s">
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="R5" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="R5" s="12" t="s">
-        <v>168</v>
-      </c>
       <c r="S5" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="T5" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="T5" s="15">
+      <c r="U5" s="15">
         <v>1720</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="V5" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="V5" s="12"/>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="12"/>
+      <c r="X5" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="X5" s="13" t="s">
+      <c r="Y5" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Z5" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="Z5" s="13" t="s">
+      <c r="AA5" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="AA5" s="12"/>
       <c r="AB5" s="12"/>
       <c r="AC5" s="12"/>
       <c r="AD5" s="12"/>
@@ -1905,41 +1917,42 @@
       <c r="AL5" s="12"/>
       <c r="AM5" s="12"/>
       <c r="AN5" s="12"/>
-      <c r="AO5" s="13" t="s">
+      <c r="AO5" s="12"/>
+      <c r="AP5" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="AP5" s="13" t="s">
+      <c r="AQ5" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="AQ5" s="13" t="s">
+      <c r="AR5" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AR5" s="13" t="s">
+      <c r="AS5" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AS5" s="13" t="s">
+      <c r="AT5" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="13" t="s">
+      <c r="AU5" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="13" t="s">
+      <c r="AV5" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="13" t="s">
+      <c r="AW5" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="AW5" s="13" t="s">
+      <c r="AX5" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AX5" s="13" t="s">
+      <c r="AY5" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AY5" s="14" t="s">
+      <c r="AZ5" s="14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>5</v>
       </c>
@@ -1955,68 +1968,68 @@
       <c r="E6" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="21"/>
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="G6" s="1">
-        <v>32.21</v>
-      </c>
       <c r="H6" s="1">
+        <v>32.39</v>
+      </c>
+      <c r="I6" s="1">
         <v>100</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>64.92</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>100</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>45.2</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>100</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>12.53</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>100</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="R6" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="S6" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="S6" s="12" t="s">
+      <c r="T6" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="T6" s="15">
+      <c r="U6" s="15">
         <v>1896</v>
       </c>
-      <c r="U6" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="V6" s="12"/>
-      <c r="W6" s="13" t="s">
+      <c r="V6" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="W6" s="12"/>
+      <c r="X6" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="X6" s="13" t="s">
+      <c r="Y6" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="Y6" s="13" t="s">
+      <c r="Z6" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Z6" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA6" s="12"/>
+      <c r="AA6" s="13" t="s">
+        <v>165</v>
+      </c>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -2030,41 +2043,42 @@
       <c r="AL6" s="12"/>
       <c r="AM6" s="12"/>
       <c r="AN6" s="12"/>
-      <c r="AO6" s="13">
+      <c r="AO6" s="12"/>
+      <c r="AP6" s="13">
         <v>10</v>
       </c>
-      <c r="AP6" s="13">
+      <c r="AQ6" s="13">
         <v>46.85</v>
       </c>
-      <c r="AQ6" s="13">
+      <c r="AR6" s="13">
         <v>54.5</v>
       </c>
-      <c r="AR6" s="13">
+      <c r="AS6" s="13">
         <v>2</v>
       </c>
-      <c r="AS6" s="13" t="s">
+      <c r="AT6" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="AT6" s="13">
+      <c r="AU6" s="13">
         <v>11.5</v>
       </c>
-      <c r="AU6" s="13">
+      <c r="AV6" s="13">
         <v>50</v>
       </c>
-      <c r="AV6" s="13" t="s">
+      <c r="AW6" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AW6" s="13">
+      <c r="AX6" s="13">
         <v>31.48</v>
       </c>
-      <c r="AX6" s="13">
+      <c r="AY6" s="13">
         <v>21.193000000000001</v>
       </c>
-      <c r="AY6" s="14">
+      <c r="AZ6" s="14">
         <v>8944</v>
       </c>
     </row>
-    <row r="7" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26">
         <v>6</v>
       </c>
@@ -2080,68 +2094,70 @@
       <c r="E7" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="F7" s="2">
-        <v>46.14</v>
+      <c r="F7" s="22" t="s">
+        <v>175</v>
       </c>
       <c r="G7" s="2">
-        <v>44.56</v>
+        <v>54.57</v>
       </c>
       <c r="H7" s="2">
+        <v>51.68</v>
+      </c>
+      <c r="I7" s="2">
         <v>79.56</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>59.42</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>56.6</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>57.05</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>47.71</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>47.4</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>18.07</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="P7" s="28" t="s">
+      <c r="Q7" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="Q7" s="16" t="s">
+      <c r="R7" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="R7" s="16" t="s">
-        <v>172</v>
-      </c>
       <c r="S7" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="T7" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="T7" s="17">
+      <c r="U7" s="17">
         <v>1750</v>
       </c>
-      <c r="U7" s="16" t="s">
+      <c r="V7" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="V7" s="16"/>
-      <c r="W7" s="18" t="s">
+      <c r="W7" s="16"/>
+      <c r="X7" s="18" t="s">
         <v>126</v>
-      </c>
-      <c r="X7" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="Y7" s="18" t="s">
         <v>127</v>
       </c>
       <c r="Z7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA7" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="AA7" s="16"/>
       <c r="AB7" s="16"/>
       <c r="AC7" s="16"/>
       <c r="AD7" s="16"/>
@@ -2155,42 +2171,43 @@
       <c r="AL7" s="16"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
-      <c r="AO7" s="18" t="s">
+      <c r="AO7" s="16"/>
+      <c r="AP7" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="AP7" s="18" t="s">
+      <c r="AQ7" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="AQ7" s="18" t="s">
+      <c r="AR7" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="AR7" s="18" t="s">
+      <c r="AS7" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="AS7" s="18" t="s">
+      <c r="AT7" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="AT7" s="18" t="s">
+      <c r="AU7" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="AU7" s="18" t="s">
+      <c r="AV7" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="AV7" s="18" t="s">
+      <c r="AW7" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="AW7" s="18" t="s">
+      <c r="AX7" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="AX7" s="18" t="s">
+      <c r="AY7" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="AY7" s="19" t="s">
+      <c r="AZ7" s="19" t="s">
         <v>152</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AZ1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261A08FB-9AAF-4F64-B6DC-DA18C87F3602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D98CBF-344F-4D5D-AC1E-EB895AB5BCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AZ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$BB$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="178">
   <si>
     <t>id</t>
   </si>
@@ -594,6 +594,12 @@
   </si>
   <si>
     <t>data/VIDEOS/CHICOASEN.mp4</t>
+  </si>
+  <si>
+    <t>avanfinReal</t>
+  </si>
+  <si>
+    <t>avanfinProg</t>
   </si>
 </sst>
 </file>
@@ -880,7 +886,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -920,8 +926,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1227,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:BB7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1238,43 +1242,44 @@
     <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17" bestFit="1" customWidth="1"/>
-    <col min="42" max="48" width="16" bestFit="1" customWidth="1"/>
-    <col min="49" max="52" width="16" customWidth="1"/>
+    <col min="9" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17" bestFit="1" customWidth="1"/>
+    <col min="44" max="50" width="16" bestFit="1" customWidth="1"/>
+    <col min="51" max="54" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1300,139 +1305,145 @@
         <v>6</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AN1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AO1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AS1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="5" t="s">
+      <c r="AT1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="5" t="s">
+      <c r="AU1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="5" t="s">
+      <c r="AV1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="5" t="s">
+      <c r="AW1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="5" t="s">
+      <c r="AX1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="5" t="s">
+      <c r="AY1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="5" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="5" t="s">
+      <c r="BA1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -1456,106 +1467,110 @@
         <v>32.17</v>
       </c>
       <c r="I2" s="7">
+        <v>53</v>
+      </c>
+      <c r="J2" s="7">
+        <v>40</v>
+      </c>
+      <c r="K2" s="7">
         <v>6.36</v>
       </c>
-      <c r="J2" s="7">
+      <c r="L2" s="7">
         <v>6.46</v>
       </c>
-      <c r="K2" s="7">
+      <c r="M2" s="7">
         <v>19.440000000000001</v>
       </c>
-      <c r="L2" s="7">
+      <c r="N2" s="7">
         <v>17.86</v>
       </c>
-      <c r="M2" s="7">
+      <c r="O2" s="7">
         <v>10.28</v>
       </c>
-      <c r="N2" s="7">
+      <c r="P2" s="7">
         <v>7.85</v>
       </c>
-      <c r="O2" s="7">
+      <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="P2" s="7">
+      <c r="R2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="T2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="U2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="U2" s="9">
+      <c r="W2" s="9">
         <v>728</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="X2" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="Y2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="Z2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="AA2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="AB2" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AC2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AD2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AE2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AF2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AG2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AH2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AG2" s="10" t="s">
+      <c r="AI2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AH2" s="9" t="s">
+      <c r="AJ2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AK2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AL2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AM2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AN2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="AM2" s="9" t="s">
+      <c r="AO2" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AN2" s="9" t="s">
+      <c r="AP2" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AO2" s="9" t="s">
+      <c r="AQ2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AP2" s="10"/>
-      <c r="AQ2" s="10"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="10"/>
       <c r="AT2" s="10"/>
@@ -1564,9 +1579,11 @@
       <c r="AW2" s="10"/>
       <c r="AX2" s="10"/>
       <c r="AY2" s="10"/>
-      <c r="AZ2" s="11"/>
+      <c r="AZ2" s="10"/>
+      <c r="BA2" s="10"/>
+      <c r="BB2" s="11"/>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="25">
         <v>2</v>
       </c>
@@ -1590,106 +1607,110 @@
         <v>9.6300000000000008</v>
       </c>
       <c r="I3" s="1">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1">
         <v>2.87</v>
       </c>
-      <c r="J3" s="1">
+      <c r="L3" s="1">
         <v>3.21</v>
       </c>
-      <c r="K3" s="1">
+      <c r="M3" s="1">
         <v>5.97</v>
       </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>5.37</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>0.91</v>
       </c>
-      <c r="N3" s="1">
+      <c r="P3" s="1">
         <v>1.05</v>
       </c>
-      <c r="O3" s="1">
+      <c r="Q3" s="1">
         <v>0</v>
       </c>
-      <c r="P3" s="1">
+      <c r="R3" s="1">
         <v>0</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="S3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="T3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="U3" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="V3" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="U3" s="12">
+      <c r="W3" s="12">
         <v>730</v>
       </c>
-      <c r="V3" s="12" t="s">
+      <c r="X3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="W3" s="13" t="s">
+      <c r="Y3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="X3" s="13" t="s">
+      <c r="Z3" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="AA3" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="AB3" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AA3" s="13" t="s">
+      <c r="AC3" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AB3" s="13" t="s">
+      <c r="AD3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AE3" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="AD3" s="13" t="s">
+      <c r="AF3" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AG3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AF3" s="13" t="s">
+      <c r="AH3" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AG3" s="13" t="s">
+      <c r="AI3" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AH3" s="12" t="s">
+      <c r="AJ3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="AI3" s="13" t="s">
+      <c r="AK3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AJ3" s="13" t="s">
+      <c r="AL3" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AK3" s="13" t="s">
+      <c r="AM3" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AL3" s="13" t="s">
+      <c r="AN3" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="AM3" s="12" t="s">
+      <c r="AO3" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AN3" s="12" t="s">
+      <c r="AP3" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AO3" s="12" t="s">
+      <c r="AQ3" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AP3" s="13"/>
-      <c r="AQ3" s="13"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
@@ -1698,9 +1719,11 @@
       <c r="AW3" s="13"/>
       <c r="AX3" s="13"/>
       <c r="AY3" s="13"/>
-      <c r="AZ3" s="14"/>
+      <c r="AZ3" s="13"/>
+      <c r="BA3" s="13"/>
+      <c r="BB3" s="14"/>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>3</v>
       </c>
@@ -1724,62 +1747,66 @@
         <v>84.36</v>
       </c>
       <c r="I4" s="1">
-        <v>100</v>
+        <v>81.39</v>
       </c>
       <c r="J4" s="1">
-        <v>99.63</v>
+        <v>72.08</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
       </c>
       <c r="L4" s="1">
+        <v>99.63</v>
+      </c>
+      <c r="M4" s="1">
         <v>100</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
+        <v>100</v>
+      </c>
+      <c r="O4" s="1">
         <v>83.08</v>
       </c>
-      <c r="N4" s="1">
+      <c r="P4" s="1">
         <v>92.58</v>
       </c>
-      <c r="O4" s="1">
+      <c r="Q4" s="1">
         <v>25.84</v>
       </c>
-      <c r="P4" s="1">
+      <c r="R4" s="1">
         <v>15.41</v>
       </c>
-      <c r="Q4" s="27" t="s">
+      <c r="S4" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="U4" s="15">
+      <c r="W4" s="15">
         <v>1420</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="X4" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="W4" s="12"/>
-      <c r="X4" s="13" t="s">
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="Y4" s="13" t="s">
+      <c r="AA4" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="Z4" s="13" t="s">
+      <c r="AB4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AA4" s="13" t="s">
+      <c r="AC4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -1792,41 +1819,43 @@
       <c r="AM4" s="12"/>
       <c r="AN4" s="12"/>
       <c r="AO4" s="12"/>
-      <c r="AP4" s="13" t="s">
+      <c r="AP4" s="12"/>
+      <c r="AQ4" s="12"/>
+      <c r="AR4" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AQ4" s="13" t="s">
+      <c r="AS4" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AR4" s="13" t="s">
+      <c r="AT4" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="AS4" s="13" t="s">
+      <c r="AU4" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AT4" s="13" t="s">
+      <c r="AV4" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="AU4" s="13" t="s">
+      <c r="AW4" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="AV4" s="13" t="s">
+      <c r="AX4" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="AW4" s="13" t="s">
+      <c r="AY4" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AX4" s="13" t="s">
+      <c r="AZ4" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AY4" s="13" t="s">
+      <c r="BA4" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="AZ4" s="14" t="s">
+      <c r="BB4" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -1850,62 +1879,66 @@
         <v>74.47</v>
       </c>
       <c r="I5" s="1">
-        <v>100</v>
+        <v>63.79</v>
       </c>
       <c r="J5" s="1">
-        <v>100</v>
+        <v>62.56</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
       </c>
       <c r="L5" s="1">
+        <v>100</v>
+      </c>
+      <c r="M5" s="1">
+        <v>100</v>
+      </c>
+      <c r="N5" s="1">
         <v>93.19</v>
       </c>
-      <c r="M5" s="1">
+      <c r="O5" s="1">
         <v>93.37</v>
       </c>
-      <c r="N5" s="1">
+      <c r="P5" s="1">
         <v>63.5</v>
       </c>
-      <c r="O5" s="1">
+      <c r="Q5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="1">
+      <c r="R5" s="1">
         <v>0</v>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="S5" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="T5" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="U5" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="V5" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="U5" s="15">
+      <c r="W5" s="15">
         <v>1720</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="X5" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="W5" s="12"/>
-      <c r="X5" s="13" t="s">
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="AA5" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="Z5" s="13" t="s">
+      <c r="AB5" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="AA5" s="13" t="s">
+      <c r="AC5" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
       <c r="AD5" s="12"/>
       <c r="AE5" s="12"/>
       <c r="AF5" s="12"/>
@@ -1918,41 +1951,43 @@
       <c r="AM5" s="12"/>
       <c r="AN5" s="12"/>
       <c r="AO5" s="12"/>
-      <c r="AP5" s="13" t="s">
+      <c r="AP5" s="12"/>
+      <c r="AQ5" s="12"/>
+      <c r="AR5" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="AQ5" s="13" t="s">
+      <c r="AS5" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="AR5" s="13" t="s">
+      <c r="AT5" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AS5" s="13" t="s">
+      <c r="AU5" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AT5" s="13" t="s">
+      <c r="AV5" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AU5" s="13" t="s">
+      <c r="AW5" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="AV5" s="13" t="s">
+      <c r="AX5" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="AW5" s="13" t="s">
+      <c r="AY5" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="AX5" s="13" t="s">
+      <c r="AZ5" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AY5" s="13" t="s">
+      <c r="BA5" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AZ5" s="14" t="s">
+      <c r="BB5" s="14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>5</v>
       </c>
@@ -1979,59 +2014,63 @@
         <v>100</v>
       </c>
       <c r="J6" s="1">
-        <v>64.92</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
       </c>
       <c r="L6" s="1">
-        <v>45.2</v>
+        <v>64.92</v>
       </c>
       <c r="M6" s="1">
         <v>100</v>
       </c>
       <c r="N6" s="1">
-        <v>12.53</v>
+        <v>45.2</v>
       </c>
       <c r="O6" s="1">
         <v>100</v>
       </c>
       <c r="P6" s="1">
+        <v>12.53</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>100</v>
+      </c>
+      <c r="R6" s="1">
         <v>0</v>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="S6" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="T6" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="S6" s="12" t="s">
+      <c r="U6" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="V6" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="U6" s="15">
+      <c r="W6" s="15">
         <v>1896</v>
       </c>
-      <c r="V6" s="12" t="s">
+      <c r="X6" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="W6" s="12"/>
-      <c r="X6" s="13" t="s">
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="Y6" s="13" t="s">
+      <c r="AA6" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="Z6" s="13" t="s">
+      <c r="AB6" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AA6" s="13" t="s">
+      <c r="AC6" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -2044,41 +2083,43 @@
       <c r="AM6" s="12"/>
       <c r="AN6" s="12"/>
       <c r="AO6" s="12"/>
-      <c r="AP6" s="13">
+      <c r="AP6" s="12"/>
+      <c r="AQ6" s="12"/>
+      <c r="AR6" s="13">
         <v>10</v>
       </c>
-      <c r="AQ6" s="13">
+      <c r="AS6" s="13">
         <v>46.85</v>
       </c>
-      <c r="AR6" s="13">
+      <c r="AT6" s="13">
         <v>54.5</v>
       </c>
-      <c r="AS6" s="13">
+      <c r="AU6" s="13">
         <v>2</v>
       </c>
-      <c r="AT6" s="13" t="s">
+      <c r="AV6" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="AU6" s="13">
+      <c r="AW6" s="13">
         <v>11.5</v>
       </c>
-      <c r="AV6" s="13">
+      <c r="AX6" s="13">
         <v>50</v>
       </c>
-      <c r="AW6" s="13" t="s">
+      <c r="AY6" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AX6" s="13">
+      <c r="AZ6" s="13">
         <v>31.48</v>
       </c>
-      <c r="AY6" s="13">
+      <c r="BA6" s="13">
         <v>21.193000000000001</v>
       </c>
-      <c r="AZ6" s="14">
+      <c r="BB6" s="14">
         <v>8944</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26">
         <v>6</v>
       </c>
@@ -2104,62 +2145,66 @@
         <v>51.68</v>
       </c>
       <c r="I7" s="2">
+        <v>54.57</v>
+      </c>
+      <c r="J7" s="2">
+        <v>53.51</v>
+      </c>
+      <c r="K7" s="2">
         <v>79.56</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>59.42</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>56.6</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>57.05</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>47.71</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>47.4</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>18.07</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="Q7" s="28" t="s">
+      <c r="S7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="R7" s="16" t="s">
+      <c r="T7" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="S7" s="16" t="s">
+      <c r="U7" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="T7" s="16" t="s">
+      <c r="V7" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="U7" s="17">
+      <c r="W7" s="17">
         <v>1750</v>
       </c>
-      <c r="V7" s="16" t="s">
+      <c r="X7" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="W7" s="16"/>
-      <c r="X7" s="18" t="s">
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="Y7" s="18" t="s">
+      <c r="AA7" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="Z7" s="18" t="s">
+      <c r="AB7" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="AA7" s="18" t="s">
+      <c r="AC7" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
       <c r="AD7" s="16"/>
       <c r="AE7" s="16"/>
       <c r="AF7" s="16"/>
@@ -2172,42 +2217,44 @@
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
       <c r="AO7" s="16"/>
-      <c r="AP7" s="18" t="s">
+      <c r="AP7" s="16"/>
+      <c r="AQ7" s="16"/>
+      <c r="AR7" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="AQ7" s="18" t="s">
+      <c r="AS7" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="AR7" s="18" t="s">
+      <c r="AT7" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="AS7" s="18" t="s">
+      <c r="AU7" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="AT7" s="18" t="s">
+      <c r="AV7" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="AU7" s="18" t="s">
+      <c r="AW7" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="AV7" s="18" t="s">
+      <c r="AX7" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="AW7" s="18" t="s">
+      <c r="AY7" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="AX7" s="18" t="s">
+      <c r="AZ7" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="AY7" s="18" t="s">
+      <c r="BA7" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="AZ7" s="19" t="s">
+      <c r="BB7" s="19" t="s">
         <v>152</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BB1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D98CBF-344F-4D5D-AC1E-EB895AB5BCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405BDD11-9B82-48DB-8B14-C39C3AAF47F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="183">
   <si>
     <t>id</t>
   </si>
@@ -600,6 +600,21 @@
   </si>
   <si>
     <t>avanfinProg</t>
+  </si>
+  <si>
+    <t>data/VIDEOS/PPSECIII.mp4</t>
+  </si>
+  <si>
+    <t>data/VIDEOS/PPSECIV.mp4</t>
+  </si>
+  <si>
+    <t>data/VIDEOS/SANTAMARIA.mp4</t>
+  </si>
+  <si>
+    <t>data/VIDEOS/PICACHOS.mp4</t>
+  </si>
+  <si>
+    <t>data/VIDEOS/AMATA.mp4</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1474,9 @@
       <c r="E2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20" t="s">
+        <v>178</v>
+      </c>
       <c r="G2" s="7">
         <v>36.08</v>
       </c>
@@ -1599,7 +1616,9 @@
       <c r="E3" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="21"/>
+      <c r="F3" s="21" t="s">
+        <v>179</v>
+      </c>
       <c r="G3" s="1">
         <v>9.75</v>
       </c>
@@ -1739,7 +1758,9 @@
       <c r="E4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="s">
+        <v>180</v>
+      </c>
       <c r="G4" s="1">
         <v>81.39</v>
       </c>
@@ -1871,7 +1892,9 @@
       <c r="E5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="21"/>
+      <c r="F5" s="21" t="s">
+        <v>181</v>
+      </c>
       <c r="G5" s="1">
         <v>93.3</v>
       </c>
@@ -2003,7 +2026,9 @@
       <c r="E6" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="21" t="s">
+        <v>182</v>
+      </c>
       <c r="G6" s="1">
         <v>100</v>
       </c>

--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405BDD11-9B82-48DB-8B14-C39C3AAF47F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0CCD30-B8A7-439E-B9C8-B515510A21E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -603,18 +603,6 @@
   </si>
   <si>
     <t>data/VIDEOS/PPSECIII.mp4</t>
-  </si>
-  <si>
-    <t>data/VIDEOS/PPSECIV.mp4</t>
-  </si>
-  <si>
-    <t>data/VIDEOS/SANTAMARIA.mp4</t>
-  </si>
-  <si>
-    <t>data/VIDEOS/PICACHOS.mp4</t>
-  </si>
-  <si>
-    <t>data/VIDEOS/AMATA.mp4</t>
   </si>
 </sst>
 </file>
@@ -1616,9 +1604,7 @@
       <c r="E3" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>179</v>
-      </c>
+      <c r="F3" s="21"/>
       <c r="G3" s="1">
         <v>9.75</v>
       </c>
@@ -1758,9 +1744,7 @@
       <c r="E4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>180</v>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="1">
         <v>81.39</v>
       </c>
@@ -1892,9 +1876,7 @@
       <c r="E5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>181</v>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="1">
         <v>93.3</v>
       </c>
@@ -2026,9 +2008,7 @@
       <c r="E6" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>182</v>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="1">
         <v>100</v>
       </c>

--- a/cartera-cpel/data/datos_proyectos.xlsx
+++ b/cartera-cpel/data/datos_proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0CCD30-B8A7-439E-B9C8-B515510A21E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFAA43F-E372-4F18-A174-C0471DAC3112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="178">
   <si>
     <t>id</t>
   </si>
@@ -600,9 +600,6 @@
   </si>
   <si>
     <t>avanfinProg</t>
-  </si>
-  <si>
-    <t>data/VIDEOS/PPSECIII.mp4</t>
   </si>
 </sst>
 </file>
@@ -1462,9 +1459,7 @@
       <c r="E2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>178</v>
-      </c>
+      <c r="F2" s="20"/>
       <c r="G2" s="7">
         <v>36.08</v>
       </c>
